--- a/research/traditional_assets/database/data/croatia/croatia_diversified.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_diversified.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08898776259608254</v>
+        <v>0.0888644846234096</v>
       </c>
       <c r="C2">
-        <v>1488.849328499359</v>
+        <v>1478.018253940651</v>
       </c>
       <c r="D2">
-        <v>1338.949328499359</v>
+        <v>1342.782253940651</v>
       </c>
       <c r="E2">
-        <v>-303.5</v>
+        <v>-288.836</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>14.664</v>
       </c>
       <c r="G2">
         <v>149.9</v>
@@ -1451,28 +1451,28 @@
         <v>145.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.7375992</v>
       </c>
       <c r="N2">
-        <v>145.1</v>
+        <v>144.3624008</v>
       </c>
       <c r="O2">
-        <v>26.118</v>
+        <v>25.985232144</v>
       </c>
       <c r="P2">
-        <v>118.982</v>
+        <v>118.377168656</v>
       </c>
       <c r="Q2">
-        <v>196.782</v>
+        <v>196.177168656</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08898776259608254</v>
+        <v>0.08934547941758544</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429368</v>
+        <v>0.7342393413571914</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>196.7193022985925</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0888644846234096</v>
+        <v>0.08874120665073665</v>
       </c>
       <c r="C3">
-        <v>1478.018253940651</v>
+        <v>1467.209186927361</v>
       </c>
       <c r="D3">
-        <v>1342.782253940651</v>
+        <v>1346.637186927361</v>
       </c>
       <c r="E3">
-        <v>-288.836</v>
+        <v>-274.172</v>
       </c>
       <c r="F3">
-        <v>14.664</v>
+        <v>29.328</v>
       </c>
       <c r="G3">
         <v>149.9</v>
@@ -1533,28 +1533,28 @@
         <v>145.1</v>
       </c>
       <c r="M3">
-        <v>0.7375992</v>
+        <v>1.4751984</v>
       </c>
       <c r="N3">
-        <v>144.3624008</v>
+        <v>143.6248016</v>
       </c>
       <c r="O3">
-        <v>25.985232144</v>
+        <v>25.852464288</v>
       </c>
       <c r="P3">
-        <v>118.377168656</v>
+        <v>117.772337312</v>
       </c>
       <c r="Q3">
-        <v>196.177168656</v>
+        <v>195.572337312</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08934547941758544</v>
+        <v>0.08971049658238434</v>
       </c>
       <c r="T3">
-        <v>0.7342393413571914</v>
+        <v>0.7403940551472472</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>196.7193022985925</v>
+        <v>98.35965114929627</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08874120665073665</v>
+        <v>0.0886179286780637</v>
       </c>
       <c r="C4">
-        <v>1467.209186927361</v>
+        <v>1456.422317546607</v>
       </c>
       <c r="D4">
-        <v>1346.637186927361</v>
+        <v>1350.514317546606</v>
       </c>
       <c r="E4">
-        <v>-274.172</v>
+        <v>-259.508</v>
       </c>
       <c r="F4">
-        <v>29.328</v>
+        <v>43.992</v>
       </c>
       <c r="G4">
         <v>149.9</v>
@@ -1615,28 +1615,28 @@
         <v>145.1</v>
       </c>
       <c r="M4">
-        <v>1.4751984</v>
+        <v>2.2127976</v>
       </c>
       <c r="N4">
-        <v>143.6248016</v>
+        <v>142.8872024</v>
       </c>
       <c r="O4">
-        <v>25.852464288</v>
+        <v>25.71969643200001</v>
       </c>
       <c r="P4">
-        <v>117.772337312</v>
+        <v>117.167505968</v>
       </c>
       <c r="Q4">
-        <v>195.572337312</v>
+        <v>194.967505968</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08971049658238434</v>
+        <v>0.09008303987429248</v>
       </c>
       <c r="T4">
-        <v>0.7403940551472472</v>
+        <v>0.7466756702525619</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>98.35965114929627</v>
+        <v>65.57310076619753</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0886179286780637</v>
+        <v>0.08849465070539075</v>
       </c>
       <c r="C5">
-        <v>1456.422317546607</v>
+        <v>1445.657838080965</v>
       </c>
       <c r="D5">
-        <v>1350.514317546606</v>
+        <v>1354.413838080965</v>
       </c>
       <c r="E5">
-        <v>-259.508</v>
+        <v>-244.844</v>
       </c>
       <c r="F5">
-        <v>43.992</v>
+        <v>58.65600000000001</v>
       </c>
       <c r="G5">
         <v>149.9</v>
@@ -1697,28 +1697,28 @@
         <v>145.1</v>
       </c>
       <c r="M5">
-        <v>2.2127976</v>
+        <v>2.9503968</v>
       </c>
       <c r="N5">
-        <v>142.8872024</v>
+        <v>142.1496032</v>
       </c>
       <c r="O5">
-        <v>25.71969643200001</v>
+        <v>25.58692857600001</v>
       </c>
       <c r="P5">
-        <v>117.167505968</v>
+        <v>116.562674624</v>
       </c>
       <c r="Q5">
-        <v>194.967505968</v>
+        <v>194.362674624</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09008303987429248</v>
+        <v>0.09046334448478204</v>
       </c>
       <c r="T5">
-        <v>0.7466756702525619</v>
+        <v>0.7530881523392372</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>65.57310076619753</v>
+        <v>49.17982557464814</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08849465070539075</v>
+        <v>0.08837137273271781</v>
       </c>
       <c r="C6">
-        <v>1445.657838080965</v>
+        <v>1434.915943040256</v>
       </c>
       <c r="D6">
-        <v>1354.413838080965</v>
+        <v>1358.335943040256</v>
       </c>
       <c r="E6">
-        <v>-244.844</v>
+        <v>-230.18</v>
       </c>
       <c r="F6">
-        <v>58.65600000000001</v>
+        <v>73.32000000000001</v>
       </c>
       <c r="G6">
         <v>149.9</v>
@@ -1779,28 +1779,28 @@
         <v>145.1</v>
       </c>
       <c r="M6">
-        <v>2.9503968</v>
+        <v>3.687996</v>
       </c>
       <c r="N6">
-        <v>142.1496032</v>
+        <v>141.412004</v>
       </c>
       <c r="O6">
-        <v>25.58692857600001</v>
+        <v>25.45416072</v>
       </c>
       <c r="P6">
-        <v>116.562674624</v>
+        <v>115.95784328</v>
       </c>
       <c r="Q6">
-        <v>194.362674624</v>
+        <v>193.75784328</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09046334448478204</v>
+        <v>0.090851655508124</v>
       </c>
       <c r="T6">
-        <v>0.7530881523392372</v>
+        <v>0.7596356340487899</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>49.17982557464814</v>
+        <v>39.34386045971851</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08837137273271781</v>
+        <v>0.08824809476004486</v>
       </c>
       <c r="C7">
-        <v>1434.915943040256</v>
+        <v>1424.196829193884</v>
       </c>
       <c r="D7">
-        <v>1358.335943040256</v>
+        <v>1362.280829193884</v>
       </c>
       <c r="E7">
-        <v>-230.18</v>
+        <v>-215.516</v>
       </c>
       <c r="F7">
-        <v>73.32000000000001</v>
+        <v>87.98400000000001</v>
       </c>
       <c r="G7">
         <v>149.9</v>
@@ -1861,28 +1861,28 @@
         <v>145.1</v>
       </c>
       <c r="M7">
-        <v>3.687996</v>
+        <v>4.4255952</v>
       </c>
       <c r="N7">
-        <v>141.412004</v>
+        <v>140.6744048</v>
       </c>
       <c r="O7">
-        <v>25.45416072</v>
+        <v>25.321392864</v>
       </c>
       <c r="P7">
-        <v>115.95784328</v>
+        <v>115.353011936</v>
       </c>
       <c r="Q7">
-        <v>193.75784328</v>
+        <v>193.153011936</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.090851655508124</v>
+        <v>0.09124822846813282</v>
       </c>
       <c r="T7">
-        <v>0.7596356340487899</v>
+        <v>0.7663224238798224</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>39.34386045971851</v>
+        <v>32.78655038309876</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08824809476004486</v>
+        <v>0.0881248167873719</v>
       </c>
       <c r="C8">
-        <v>1424.196829193884</v>
+        <v>1413.500695603748</v>
       </c>
       <c r="D8">
-        <v>1362.280829193884</v>
+        <v>1366.248695603748</v>
       </c>
       <c r="E8">
-        <v>-215.516</v>
+        <v>-200.852</v>
       </c>
       <c r="F8">
-        <v>87.98400000000001</v>
+        <v>102.648</v>
       </c>
       <c r="G8">
         <v>149.9</v>
@@ -1943,28 +1943,28 @@
         <v>145.1</v>
       </c>
       <c r="M8">
-        <v>4.4255952</v>
+        <v>5.163194399999999</v>
       </c>
       <c r="N8">
-        <v>140.6744048</v>
+        <v>139.9368056</v>
       </c>
       <c r="O8">
-        <v>25.321392864</v>
+        <v>25.188625008</v>
       </c>
       <c r="P8">
-        <v>115.353011936</v>
+        <v>114.748180592</v>
       </c>
       <c r="Q8">
-        <v>193.153011936</v>
+        <v>192.548180592</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09124822846813282</v>
+        <v>0.09165332987889452</v>
       </c>
       <c r="T8">
-        <v>0.7663224238798224</v>
+        <v>0.7731530156427052</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.78655038309876</v>
+        <v>28.10275747122751</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0881248167873719</v>
+        <v>0.08800153881469897</v>
       </c>
       <c r="C9">
-        <v>1413.500695603748</v>
+        <v>1402.827743657721</v>
       </c>
       <c r="D9">
-        <v>1366.248695603748</v>
+        <v>1370.239743657721</v>
       </c>
       <c r="E9">
-        <v>-200.852</v>
+        <v>-186.188</v>
       </c>
       <c r="F9">
-        <v>102.648</v>
+        <v>117.312</v>
       </c>
       <c r="G9">
         <v>149.9</v>
@@ -2025,28 +2025,28 @@
         <v>145.1</v>
       </c>
       <c r="M9">
-        <v>5.1631944</v>
+        <v>5.9007936</v>
       </c>
       <c r="N9">
-        <v>139.9368056</v>
+        <v>139.1992064</v>
       </c>
       <c r="O9">
-        <v>25.188625008</v>
+        <v>25.05585715200001</v>
       </c>
       <c r="P9">
-        <v>114.748180592</v>
+        <v>114.143349248</v>
       </c>
       <c r="Q9">
-        <v>192.548180592</v>
+        <v>191.943349248</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09165332987889452</v>
+        <v>0.0920672378420641</v>
       </c>
       <c r="T9">
-        <v>0.7731530156427052</v>
+        <v>0.7801320985308681</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.10275747122751</v>
+        <v>24.58991278732407</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08800153881469897</v>
+        <v>0.08787826084202602</v>
       </c>
       <c r="C10">
-        <v>1402.827743657721</v>
+        <v>1392.178177103728</v>
       </c>
       <c r="D10">
-        <v>1370.239743657721</v>
+        <v>1374.254177103728</v>
       </c>
       <c r="E10">
-        <v>-186.188</v>
+        <v>-171.524</v>
       </c>
       <c r="F10">
-        <v>117.312</v>
+        <v>131.976</v>
       </c>
       <c r="G10">
         <v>149.9</v>
@@ -2107,28 +2107,28 @@
         <v>145.1</v>
       </c>
       <c r="M10">
-        <v>5.9007936</v>
+        <v>6.638392799999999</v>
       </c>
       <c r="N10">
-        <v>139.1992064</v>
+        <v>138.4616072</v>
       </c>
       <c r="O10">
-        <v>25.05585715200001</v>
+        <v>24.923089296</v>
       </c>
       <c r="P10">
-        <v>114.143349248</v>
+        <v>113.538517904</v>
       </c>
       <c r="Q10">
-        <v>191.943349248</v>
+        <v>191.338517904</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0920672378420641</v>
+        <v>0.09249024268354507</v>
       </c>
       <c r="T10">
-        <v>0.7801320985308681</v>
+        <v>0.7872645678561333</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.58991278732407</v>
+        <v>21.85770025539918</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08787826084202602</v>
+        <v>0.08775498286935307</v>
       </c>
       <c r="C11">
-        <v>1392.178177103728</v>
+        <v>1381.552202084413</v>
       </c>
       <c r="D11">
-        <v>1374.254177103728</v>
+        <v>1378.292202084413</v>
       </c>
       <c r="E11">
-        <v>-171.524</v>
+        <v>-156.86</v>
       </c>
       <c r="F11">
-        <v>131.976</v>
+        <v>146.64</v>
       </c>
       <c r="G11">
         <v>149.9</v>
@@ -2189,28 +2189,28 @@
         <v>145.1</v>
       </c>
       <c r="M11">
-        <v>6.638392799999999</v>
+        <v>7.375991999999999</v>
       </c>
       <c r="N11">
-        <v>138.4616072</v>
+        <v>137.724008</v>
       </c>
       <c r="O11">
-        <v>24.923089296</v>
+        <v>24.79032144</v>
       </c>
       <c r="P11">
-        <v>113.538517904</v>
+        <v>112.93368656</v>
       </c>
       <c r="Q11">
-        <v>191.338517904</v>
+        <v>190.73368656</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09249024268354507</v>
+        <v>0.09292264763261451</v>
       </c>
       <c r="T11">
-        <v>0.7872645678561333</v>
+        <v>0.7945555364997378</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.85770025539918</v>
+        <v>19.67193022985926</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08775498286935307</v>
+        <v>0.08763170489668011</v>
       </c>
       <c r="C12">
-        <v>1381.552202084413</v>
+        <v>1370.950027172432</v>
       </c>
       <c r="D12">
-        <v>1378.292202084413</v>
+        <v>1382.354027172432</v>
       </c>
       <c r="E12">
-        <v>-156.86</v>
+        <v>-142.196</v>
       </c>
       <c r="F12">
-        <v>146.64</v>
+        <v>161.304</v>
       </c>
       <c r="G12">
         <v>149.9</v>
@@ -2271,28 +2271,28 @@
         <v>145.1</v>
       </c>
       <c r="M12">
-        <v>7.375992</v>
+        <v>8.1135912</v>
       </c>
       <c r="N12">
-        <v>137.724008</v>
+        <v>136.9864088</v>
       </c>
       <c r="O12">
-        <v>24.79032144</v>
+        <v>24.657553584</v>
       </c>
       <c r="P12">
-        <v>112.93368656</v>
+        <v>112.328855216</v>
       </c>
       <c r="Q12">
-        <v>190.73368656</v>
+        <v>190.128855216</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09292264763261451</v>
+        <v>0.09336476954683159</v>
       </c>
       <c r="T12">
-        <v>0.7945555364997378</v>
+        <v>0.8020103471353333</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.67193022985925</v>
+        <v>17.88357293623569</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08763170489668011</v>
+        <v>0.08750842692400716</v>
       </c>
       <c r="C13">
-        <v>1370.950027172432</v>
+        <v>1360.371863406356</v>
       </c>
       <c r="D13">
-        <v>1382.354027172432</v>
+        <v>1386.439863406356</v>
       </c>
       <c r="E13">
-        <v>-142.196</v>
+        <v>-127.532</v>
       </c>
       <c r="F13">
-        <v>161.304</v>
+        <v>175.968</v>
       </c>
       <c r="G13">
         <v>149.9</v>
@@ -2353,28 +2353,28 @@
         <v>145.1</v>
       </c>
       <c r="M13">
-        <v>8.1135912</v>
+        <v>8.8511904</v>
       </c>
       <c r="N13">
-        <v>136.9864088</v>
+        <v>136.2488096</v>
       </c>
       <c r="O13">
-        <v>24.657553584</v>
+        <v>24.524785728</v>
       </c>
       <c r="P13">
-        <v>112.328855216</v>
+        <v>111.724023872</v>
       </c>
       <c r="Q13">
-        <v>190.128855216</v>
+        <v>189.524023872</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09336476954683159</v>
+        <v>0.09381693968637178</v>
       </c>
       <c r="T13">
-        <v>0.8020103471353333</v>
+        <v>0.8096345852853742</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.88357293623569</v>
+        <v>16.39327519154938</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08750842692400716</v>
+        <v>0.08738514895133423</v>
       </c>
       <c r="C14">
-        <v>1360.371863406356</v>
+        <v>1349.817924327232</v>
       </c>
       <c r="D14">
-        <v>1386.439863406356</v>
+        <v>1390.549924327232</v>
       </c>
       <c r="E14">
-        <v>-127.532</v>
+        <v>-112.868</v>
       </c>
       <c r="F14">
-        <v>175.968</v>
+        <v>190.632</v>
       </c>
       <c r="G14">
         <v>149.9</v>
@@ -2435,28 +2435,28 @@
         <v>145.1</v>
       </c>
       <c r="M14">
-        <v>8.8511904</v>
+        <v>9.5887896</v>
       </c>
       <c r="N14">
-        <v>136.2488096</v>
+        <v>135.5112104</v>
       </c>
       <c r="O14">
-        <v>24.524785728</v>
+        <v>24.392017872</v>
       </c>
       <c r="P14">
-        <v>111.724023872</v>
+        <v>111.119192528</v>
       </c>
       <c r="Q14">
-        <v>189.524023872</v>
+        <v>188.919192528</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09381693968637178</v>
+        <v>0.09427950454176348</v>
       </c>
       <c r="T14">
-        <v>0.8096345852853742</v>
+        <v>0.817434093277945</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.39327519154938</v>
+        <v>15.13225402296866</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08738514895133423</v>
+        <v>0.08726187097866128</v>
       </c>
       <c r="C15">
-        <v>1349.817924327232</v>
+        <v>1339.288426015778</v>
       </c>
       <c r="D15">
-        <v>1390.549924327232</v>
+        <v>1394.684426015778</v>
       </c>
       <c r="E15">
-        <v>-112.868</v>
+        <v>-98.20399999999998</v>
       </c>
       <c r="F15">
-        <v>190.632</v>
+        <v>205.296</v>
       </c>
       <c r="G15">
         <v>149.9</v>
@@ -2517,28 +2517,28 @@
         <v>145.1</v>
       </c>
       <c r="M15">
-        <v>9.5887896</v>
+        <v>10.3263888</v>
       </c>
       <c r="N15">
-        <v>135.5112104</v>
+        <v>134.7736112</v>
       </c>
       <c r="O15">
-        <v>24.392017872</v>
+        <v>24.25925001600001</v>
       </c>
       <c r="P15">
-        <v>111.119192528</v>
+        <v>110.514361184</v>
       </c>
       <c r="Q15">
-        <v>188.919192528</v>
+        <v>188.314361184</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09427950454176348</v>
+        <v>0.09475282671937357</v>
       </c>
       <c r="T15">
-        <v>0.817434093277945</v>
+        <v>0.8254149851773196</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.13225402296866</v>
+        <v>14.05137873561375</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08726187097866128</v>
+        <v>0.08713859300598832</v>
       </c>
       <c r="C16">
-        <v>1339.288426015778</v>
+        <v>1328.783587130258</v>
       </c>
       <c r="D16">
-        <v>1394.684426015778</v>
+        <v>1398.843587130257</v>
       </c>
       <c r="E16">
-        <v>-98.20399999999998</v>
+        <v>-83.53999999999996</v>
       </c>
       <c r="F16">
-        <v>205.296</v>
+        <v>219.96</v>
       </c>
       <c r="G16">
         <v>149.9</v>
@@ -2599,28 +2599,28 @@
         <v>145.1</v>
       </c>
       <c r="M16">
-        <v>10.3263888</v>
+        <v>11.063988</v>
       </c>
       <c r="N16">
-        <v>134.7736112</v>
+        <v>134.036012</v>
       </c>
       <c r="O16">
-        <v>24.25925001600001</v>
+        <v>24.12648216000001</v>
       </c>
       <c r="P16">
-        <v>110.514361184</v>
+        <v>109.90952984</v>
       </c>
       <c r="Q16">
-        <v>188.314361184</v>
+        <v>187.70952984</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09475282671937357</v>
+        <v>0.09523728588939803</v>
       </c>
       <c r="T16">
-        <v>0.8254149851773196</v>
+        <v>0.8335836627684442</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.05137873561375</v>
+        <v>13.1146201532395</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08713859300598832</v>
+        <v>0.08721211503331536</v>
       </c>
       <c r="C17">
-        <v>1328.783587130258</v>
+        <v>1311.636115412947</v>
       </c>
       <c r="D17">
-        <v>1398.843587130257</v>
+        <v>1396.360115412947</v>
       </c>
       <c r="E17">
-        <v>-83.53999999999999</v>
+        <v>-68.87599999999998</v>
       </c>
       <c r="F17">
-        <v>219.96</v>
+        <v>234.624</v>
       </c>
       <c r="G17">
         <v>149.9</v>
@@ -2681,45 +2681,45 @@
         <v>145.1</v>
       </c>
       <c r="M17">
-        <v>11.063988</v>
+        <v>12.1535232</v>
       </c>
       <c r="N17">
-        <v>134.036012</v>
+        <v>132.9464768</v>
       </c>
       <c r="O17">
-        <v>24.12648216000001</v>
+        <v>23.930365824</v>
       </c>
       <c r="P17">
-        <v>109.90952984</v>
+        <v>109.016110976</v>
       </c>
       <c r="Q17">
-        <v>187.70952984</v>
+        <v>186.816110976</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09523728588939803</v>
+        <v>0.09573327980156592</v>
       </c>
       <c r="T17">
-        <v>0.8335836627684442</v>
+        <v>0.8419468326831669</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.18</v>
       </c>
       <c r="W17">
-        <v>0.041246</v>
+        <v>0.042476</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.1146201532395</v>
+        <v>11.93892483786101</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08721211503331536</v>
+        <v>0.08710113706064242</v>
       </c>
       <c r="C18">
-        <v>1311.636115412947</v>
+        <v>1300.724196487673</v>
       </c>
       <c r="D18">
-        <v>1396.360115412947</v>
+        <v>1400.112196487672</v>
       </c>
       <c r="E18">
-        <v>-68.87599999999998</v>
+        <v>-54.21199999999996</v>
       </c>
       <c r="F18">
-        <v>234.624</v>
+        <v>249.288</v>
       </c>
       <c r="G18">
         <v>149.9</v>
@@ -2763,28 +2763,28 @@
         <v>145.1</v>
       </c>
       <c r="M18">
-        <v>12.1535232</v>
+        <v>12.9131184</v>
       </c>
       <c r="N18">
-        <v>132.9464768</v>
+        <v>132.1868816</v>
       </c>
       <c r="O18">
-        <v>23.930365824</v>
+        <v>23.793638688</v>
       </c>
       <c r="P18">
-        <v>109.016110976</v>
+        <v>108.393242912</v>
       </c>
       <c r="Q18">
-        <v>186.816110976</v>
+        <v>186.193242912</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09573327980156592</v>
+        <v>0.09624122537426798</v>
       </c>
       <c r="T18">
-        <v>0.8419468326831669</v>
+        <v>0.8505115247645095</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.93892483786101</v>
+        <v>11.23663514151624</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08710113706064242</v>
+        <v>0.08699015908796948</v>
       </c>
       <c r="C19">
-        <v>1300.724196487673</v>
+        <v>1289.832495903876</v>
       </c>
       <c r="D19">
-        <v>1400.112196487672</v>
+        <v>1403.884495903876</v>
       </c>
       <c r="E19">
-        <v>-54.21199999999996</v>
+        <v>-39.54799999999994</v>
       </c>
       <c r="F19">
-        <v>249.288</v>
+        <v>263.9520000000001</v>
       </c>
       <c r="G19">
         <v>149.9</v>
@@ -2845,28 +2845,28 @@
         <v>145.1</v>
       </c>
       <c r="M19">
-        <v>12.9131184</v>
+        <v>13.6727136</v>
       </c>
       <c r="N19">
-        <v>132.1868816</v>
+        <v>131.4272864</v>
       </c>
       <c r="O19">
-        <v>23.793638688</v>
+        <v>23.656911552</v>
       </c>
       <c r="P19">
-        <v>108.393242912</v>
+        <v>107.770374848</v>
       </c>
       <c r="Q19">
-        <v>186.193242912</v>
+        <v>185.570374848</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09624122537426798</v>
+        <v>0.09676155986337742</v>
       </c>
       <c r="T19">
-        <v>0.8505115247645095</v>
+        <v>0.8592851117746656</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.23663514151624</v>
+        <v>10.61237763365423</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08699015908796948</v>
+        <v>0.08687918111529652</v>
       </c>
       <c r="C20">
-        <v>1289.832495903876</v>
+        <v>1278.961177524892</v>
       </c>
       <c r="D20">
-        <v>1403.884495903876</v>
+        <v>1407.677177524892</v>
       </c>
       <c r="E20">
-        <v>-39.548</v>
+        <v>-24.88399999999996</v>
       </c>
       <c r="F20">
-        <v>263.952</v>
+        <v>278.616</v>
       </c>
       <c r="G20">
         <v>149.9</v>
@@ -2927,28 +2927,28 @@
         <v>145.1</v>
       </c>
       <c r="M20">
-        <v>13.6727136</v>
+        <v>14.4323088</v>
       </c>
       <c r="N20">
-        <v>131.4272864</v>
+        <v>130.6676912</v>
       </c>
       <c r="O20">
-        <v>23.656911552</v>
+        <v>23.52018441600001</v>
       </c>
       <c r="P20">
-        <v>107.770374848</v>
+        <v>107.147506784</v>
       </c>
       <c r="Q20">
-        <v>185.570374848</v>
+        <v>184.947506784</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09676155986337739</v>
+        <v>0.09729474211765002</v>
       </c>
       <c r="T20">
-        <v>0.8592851117746654</v>
+        <v>0.8682753305628498</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.61237763365423</v>
+        <v>10.05383144240927</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08687918111529652</v>
+        <v>0.08704700314262359</v>
       </c>
       <c r="C21">
-        <v>1278.961177524892</v>
+        <v>1258.569749596677</v>
       </c>
       <c r="D21">
-        <v>1407.677177524892</v>
+        <v>1401.949749596676</v>
       </c>
       <c r="E21">
-        <v>-24.88399999999996</v>
+        <v>-10.21999999999997</v>
       </c>
       <c r="F21">
-        <v>278.616</v>
+        <v>293.28</v>
       </c>
       <c r="G21">
         <v>149.9</v>
@@ -3009,45 +3009,45 @@
         <v>145.1</v>
       </c>
       <c r="M21">
-        <v>14.4323088</v>
+        <v>15.69048</v>
       </c>
       <c r="N21">
-        <v>130.6676912</v>
+        <v>129.40952</v>
       </c>
       <c r="O21">
-        <v>23.52018441600001</v>
+        <v>23.2937136</v>
       </c>
       <c r="P21">
-        <v>107.147506784</v>
+        <v>106.1158064</v>
       </c>
       <c r="Q21">
-        <v>184.947506784</v>
+        <v>183.9158064</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09729474211765002</v>
+        <v>0.09784125392827947</v>
       </c>
       <c r="T21">
-        <v>0.8682753305628498</v>
+        <v>0.8774903048207389</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.18</v>
       </c>
       <c r="W21">
-        <v>0.042476</v>
+        <v>0.04387</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.05383144240927</v>
+        <v>9.247645706186171</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08704700314262359</v>
+        <v>0.08694996516995064</v>
       </c>
       <c r="C22">
-        <v>1258.569749596677</v>
+        <v>1247.211763609771</v>
       </c>
       <c r="D22">
-        <v>1401.949749596676</v>
+        <v>1405.255763609771</v>
       </c>
       <c r="E22">
-        <v>-10.21999999999997</v>
+        <v>4.444000000000074</v>
       </c>
       <c r="F22">
-        <v>293.28</v>
+        <v>307.9440000000001</v>
       </c>
       <c r="G22">
         <v>149.9</v>
@@ -3091,28 +3091,28 @@
         <v>145.1</v>
       </c>
       <c r="M22">
-        <v>15.69048</v>
+        <v>16.475004</v>
       </c>
       <c r="N22">
-        <v>129.40952</v>
+        <v>128.624996</v>
       </c>
       <c r="O22">
-        <v>23.2937136</v>
+        <v>23.15249928</v>
       </c>
       <c r="P22">
-        <v>106.1158064</v>
+        <v>105.47249672</v>
       </c>
       <c r="Q22">
-        <v>183.9158064</v>
+        <v>183.27249672</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09784125392827947</v>
+        <v>0.09840160148095016</v>
       </c>
       <c r="T22">
-        <v>0.8774903048207389</v>
+        <v>0.8869385695661693</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.247645706186171</v>
+        <v>8.807281624939211</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08694996516995064</v>
+        <v>0.08685292719727768</v>
       </c>
       <c r="C23">
-        <v>1247.211763609771</v>
+        <v>1235.869406661737</v>
       </c>
       <c r="D23">
-        <v>1405.255763609771</v>
+        <v>1408.577406661737</v>
       </c>
       <c r="E23">
-        <v>4.444000000000017</v>
+        <v>19.108</v>
       </c>
       <c r="F23">
-        <v>307.944</v>
+        <v>322.608</v>
       </c>
       <c r="G23">
         <v>149.9</v>
@@ -3173,28 +3173,28 @@
         <v>145.1</v>
       </c>
       <c r="M23">
-        <v>16.475004</v>
+        <v>17.259528</v>
       </c>
       <c r="N23">
-        <v>128.624996</v>
+        <v>127.840472</v>
       </c>
       <c r="O23">
-        <v>23.15249928</v>
+        <v>23.01128496</v>
       </c>
       <c r="P23">
-        <v>105.47249672</v>
+        <v>104.82918704</v>
       </c>
       <c r="Q23">
-        <v>183.27249672</v>
+        <v>182.62918704</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09840160148095016</v>
+        <v>0.09897631691958676</v>
       </c>
       <c r="T23">
-        <v>0.8869385695661693</v>
+        <v>0.8966290975102006</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.807281624939211</v>
+        <v>8.406950641987429</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08685292719727768</v>
+        <v>0.08675588922460474</v>
       </c>
       <c r="C24">
-        <v>1235.869406661737</v>
+        <v>1224.542789843573</v>
       </c>
       <c r="D24">
-        <v>1408.577406661737</v>
+        <v>1411.914789843573</v>
       </c>
       <c r="E24">
-        <v>19.108</v>
+        <v>33.77200000000005</v>
       </c>
       <c r="F24">
-        <v>322.608</v>
+        <v>337.272</v>
       </c>
       <c r="G24">
         <v>149.9</v>
@@ -3255,28 +3255,28 @@
         <v>145.1</v>
       </c>
       <c r="M24">
-        <v>17.259528</v>
+        <v>18.044052</v>
       </c>
       <c r="N24">
-        <v>127.840472</v>
+        <v>127.055948</v>
       </c>
       <c r="O24">
-        <v>23.01128496</v>
+        <v>22.87007064000001</v>
       </c>
       <c r="P24">
-        <v>104.82918704</v>
+        <v>104.18587736</v>
       </c>
       <c r="Q24">
-        <v>182.62918704</v>
+        <v>181.98587736</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09897631691958676</v>
+        <v>0.0995659600319542</v>
       </c>
       <c r="T24">
-        <v>0.8966290975102006</v>
+        <v>0.9065713274787522</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.406950641987429</v>
+        <v>8.041431048857543</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08675588922460474</v>
+        <v>0.08665885125193179</v>
       </c>
       <c r="C25">
-        <v>1224.542789843573</v>
+        <v>1213.232025301628</v>
       </c>
       <c r="D25">
-        <v>1411.914789843573</v>
+        <v>1415.268025301628</v>
       </c>
       <c r="E25">
-        <v>33.77200000000005</v>
+        <v>48.43600000000004</v>
       </c>
       <c r="F25">
-        <v>337.272</v>
+        <v>351.936</v>
       </c>
       <c r="G25">
         <v>149.9</v>
@@ -3337,28 +3337,28 @@
         <v>145.1</v>
       </c>
       <c r="M25">
-        <v>18.044052</v>
+        <v>18.828576</v>
       </c>
       <c r="N25">
-        <v>127.055948</v>
+        <v>126.271424</v>
       </c>
       <c r="O25">
-        <v>22.87007064000001</v>
+        <v>22.72885632</v>
       </c>
       <c r="P25">
-        <v>104.18587736</v>
+        <v>103.54256768</v>
       </c>
       <c r="Q25">
-        <v>181.98587736</v>
+        <v>181.34256768</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0995659600319542</v>
+        <v>0.1001711200683313</v>
       </c>
       <c r="T25">
-        <v>0.9065713274787522</v>
+        <v>0.9167751950780553</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.041431048857543</v>
+        <v>7.70637142182181</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08665885125193179</v>
+        <v>0.08672581327925884</v>
       </c>
       <c r="C26">
-        <v>1213.232025301628</v>
+        <v>1196.252391021164</v>
       </c>
       <c r="D26">
-        <v>1415.268025301628</v>
+        <v>1412.952391021164</v>
       </c>
       <c r="E26">
-        <v>48.43600000000004</v>
+        <v>63.10000000000002</v>
       </c>
       <c r="F26">
-        <v>351.936</v>
+        <v>366.6</v>
       </c>
       <c r="G26">
         <v>149.9</v>
@@ -3419,45 +3419,45 @@
         <v>145.1</v>
       </c>
       <c r="M26">
-        <v>18.828576</v>
+        <v>19.90638</v>
       </c>
       <c r="N26">
-        <v>126.271424</v>
+        <v>125.19362</v>
       </c>
       <c r="O26">
-        <v>22.72885632</v>
+        <v>22.5348516</v>
       </c>
       <c r="P26">
-        <v>103.54256768</v>
+        <v>102.6587684</v>
       </c>
       <c r="Q26">
-        <v>181.34256768</v>
+        <v>180.4587684</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1001711200683313</v>
+        <v>0.1007924177056784</v>
       </c>
       <c r="T26">
-        <v>0.9167751950780552</v>
+        <v>0.9272511658133396</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.18</v>
       </c>
       <c r="W26">
-        <v>0.04387</v>
+        <v>0.044526</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.70637142182181</v>
+        <v>7.289120372463502</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08672581327925884</v>
+        <v>0.08663533530658589</v>
       </c>
       <c r="C27">
-        <v>1196.252391021164</v>
+        <v>1184.719039192978</v>
       </c>
       <c r="D27">
-        <v>1412.952391021164</v>
+        <v>1416.083039192978</v>
       </c>
       <c r="E27">
-        <v>63.10000000000002</v>
+        <v>77.76400000000001</v>
       </c>
       <c r="F27">
-        <v>366.6</v>
+        <v>381.264</v>
       </c>
       <c r="G27">
         <v>149.9</v>
@@ -3501,28 +3501,28 @@
         <v>145.1</v>
       </c>
       <c r="M27">
-        <v>19.90638</v>
+        <v>20.7026352</v>
       </c>
       <c r="N27">
-        <v>125.19362</v>
+        <v>124.3973648</v>
       </c>
       <c r="O27">
-        <v>22.5348516</v>
+        <v>22.391525664</v>
       </c>
       <c r="P27">
-        <v>102.6587684</v>
+        <v>102.005839136</v>
       </c>
       <c r="Q27">
-        <v>180.4587684</v>
+        <v>179.805839136</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1007924177056784</v>
+        <v>0.101430507171062</v>
       </c>
       <c r="T27">
-        <v>0.9272511658133396</v>
+        <v>0.9380102708928207</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.289120372463502</v>
+        <v>7.008769588907215</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08663533530658589</v>
+        <v>0.08654485733391293</v>
       </c>
       <c r="C28">
-        <v>1184.719039192978</v>
+        <v>1173.199591190614</v>
       </c>
       <c r="D28">
-        <v>1416.083039192978</v>
+        <v>1419.227591190614</v>
       </c>
       <c r="E28">
-        <v>77.76400000000001</v>
+        <v>92.42800000000005</v>
       </c>
       <c r="F28">
-        <v>381.264</v>
+        <v>395.9280000000001</v>
       </c>
       <c r="G28">
         <v>149.9</v>
@@ -3583,28 +3583,28 @@
         <v>145.1</v>
       </c>
       <c r="M28">
-        <v>20.7026352</v>
+        <v>21.4988904</v>
       </c>
       <c r="N28">
-        <v>124.3973648</v>
+        <v>123.6011096</v>
       </c>
       <c r="O28">
-        <v>22.391525664</v>
+        <v>22.248199728</v>
       </c>
       <c r="P28">
-        <v>102.005839136</v>
+        <v>101.352909872</v>
       </c>
       <c r="Q28">
-        <v>179.805839136</v>
+        <v>179.152909872</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.101430507171062</v>
+        <v>0.1020860785396068</v>
       </c>
       <c r="T28">
-        <v>0.9380102708928207</v>
+        <v>0.9490641459744795</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.008769588907215</v>
+        <v>6.749185530058798</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08654485733391293</v>
+        <v>0.08645437936123998</v>
       </c>
       <c r="C29">
-        <v>1173.199591190614</v>
+        <v>1161.694139844658</v>
       </c>
       <c r="D29">
-        <v>1419.227591190614</v>
+        <v>1422.386139844658</v>
       </c>
       <c r="E29">
-        <v>92.42800000000005</v>
+        <v>107.092</v>
       </c>
       <c r="F29">
-        <v>395.9280000000001</v>
+        <v>410.592</v>
       </c>
       <c r="G29">
         <v>149.9</v>
@@ -3665,28 +3665,28 @@
         <v>145.1</v>
       </c>
       <c r="M29">
-        <v>21.4988904</v>
+        <v>22.2951456</v>
       </c>
       <c r="N29">
-        <v>123.6011096</v>
+        <v>122.8048544</v>
       </c>
       <c r="O29">
-        <v>22.248199728</v>
+        <v>22.104873792</v>
       </c>
       <c r="P29">
-        <v>101.352909872</v>
+        <v>100.699980608</v>
       </c>
       <c r="Q29">
-        <v>179.152909872</v>
+        <v>178.499980608</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1020860785396068</v>
+        <v>0.1027598602239444</v>
       </c>
       <c r="T29">
-        <v>0.9490641459744795</v>
+        <v>0.9604250731417401</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.749185530058798</v>
+        <v>6.508143189699556</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08645437936123998</v>
+        <v>0.08636390138856703</v>
       </c>
       <c r="C30">
-        <v>1161.694139844658</v>
+        <v>1150.202778813934</v>
       </c>
       <c r="D30">
-        <v>1422.386139844658</v>
+        <v>1425.558778813934</v>
       </c>
       <c r="E30">
-        <v>107.092</v>
+        <v>121.7560000000001</v>
       </c>
       <c r="F30">
-        <v>410.592</v>
+        <v>425.2560000000001</v>
       </c>
       <c r="G30">
         <v>149.9</v>
@@ -3747,28 +3747,28 @@
         <v>145.1</v>
       </c>
       <c r="M30">
-        <v>22.2951456</v>
+        <v>23.09140080000001</v>
       </c>
       <c r="N30">
-        <v>122.8048544</v>
+        <v>122.0085992</v>
       </c>
       <c r="O30">
-        <v>22.104873792</v>
+        <v>21.961547856</v>
       </c>
       <c r="P30">
-        <v>100.699980608</v>
+        <v>100.047051344</v>
       </c>
       <c r="Q30">
-        <v>178.499980608</v>
+        <v>177.847051344</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1027598602239444</v>
+        <v>0.1034526216740381</v>
       </c>
       <c r="T30">
-        <v>0.9604250731417401</v>
+        <v>0.972106026426388</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.508143189699556</v>
+        <v>6.283724459020259</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08636390138856703</v>
+        <v>0.08651942341589408</v>
       </c>
       <c r="C31">
-        <v>1150.202778813934</v>
+        <v>1130.094060476678</v>
       </c>
       <c r="D31">
-        <v>1425.558778813934</v>
+        <v>1420.114060476678</v>
       </c>
       <c r="E31">
-        <v>121.756</v>
+        <v>136.42</v>
       </c>
       <c r="F31">
-        <v>425.256</v>
+        <v>439.92</v>
       </c>
       <c r="G31">
         <v>149.9</v>
@@ -3829,45 +3829,45 @@
         <v>145.1</v>
       </c>
       <c r="M31">
-        <v>23.0914008</v>
+        <v>24.327576</v>
       </c>
       <c r="N31">
-        <v>122.0085992</v>
+        <v>120.772424</v>
       </c>
       <c r="O31">
-        <v>21.961547856</v>
+        <v>21.73903632</v>
       </c>
       <c r="P31">
-        <v>100.047051344</v>
+        <v>99.03338768000003</v>
       </c>
       <c r="Q31">
-        <v>177.847051344</v>
+        <v>176.83338768</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1034526216740381</v>
+        <v>0.1041651763084201</v>
       </c>
       <c r="T31">
-        <v>0.972106026426388</v>
+        <v>0.9841207212334546</v>
       </c>
       <c r="U31">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0.18</v>
       </c>
       <c r="W31">
-        <v>0.044526</v>
+        <v>0.045346</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>6.283724459020261</v>
+        <v>5.964424897901872</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08651942341589408</v>
+        <v>0.08643714544322113</v>
       </c>
       <c r="C32">
-        <v>1130.094060476678</v>
+        <v>1118.305363468214</v>
       </c>
       <c r="D32">
-        <v>1420.114060476678</v>
+        <v>1422.989363468214</v>
       </c>
       <c r="E32">
-        <v>136.42</v>
+        <v>151.084</v>
       </c>
       <c r="F32">
-        <v>439.92</v>
+        <v>454.584</v>
       </c>
       <c r="G32">
         <v>149.9</v>
@@ -3911,28 +3911,28 @@
         <v>145.1</v>
       </c>
       <c r="M32">
-        <v>24.327576</v>
+        <v>25.1384952</v>
       </c>
       <c r="N32">
-        <v>120.772424</v>
+        <v>119.9615048</v>
       </c>
       <c r="O32">
-        <v>21.73903632</v>
+        <v>21.593070864</v>
       </c>
       <c r="P32">
-        <v>99.03338768000003</v>
+        <v>98.36843393600003</v>
       </c>
       <c r="Q32">
-        <v>176.83338768</v>
+        <v>176.168433936</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1041651763084201</v>
+        <v>0.1048983847003205</v>
       </c>
       <c r="T32">
-        <v>0.9841207212334546</v>
+        <v>0.9964836680639144</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.964424897901872</v>
+        <v>5.772024094743747</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08643714544322113</v>
+        <v>0.08635486747054819</v>
       </c>
       <c r="C33">
-        <v>1118.305363468214</v>
+        <v>1106.528333325688</v>
       </c>
       <c r="D33">
-        <v>1422.989363468214</v>
+        <v>1425.876333325688</v>
       </c>
       <c r="E33">
-        <v>151.084</v>
+        <v>165.748</v>
       </c>
       <c r="F33">
-        <v>454.584</v>
+        <v>469.248</v>
       </c>
       <c r="G33">
         <v>149.9</v>
@@ -3993,28 +3993,28 @@
         <v>145.1</v>
       </c>
       <c r="M33">
-        <v>25.1384952</v>
+        <v>25.9494144</v>
       </c>
       <c r="N33">
-        <v>119.9615048</v>
+        <v>119.1505856</v>
       </c>
       <c r="O33">
-        <v>21.593070864</v>
+        <v>21.44710540800001</v>
       </c>
       <c r="P33">
-        <v>98.36843393600003</v>
+        <v>97.70348019200003</v>
       </c>
       <c r="Q33">
-        <v>176.168433936</v>
+        <v>175.503480192</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1048983847003205</v>
+        <v>0.1056531580449238</v>
       </c>
       <c r="T33">
-        <v>0.9964836680639144</v>
+        <v>1.009210230977623</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.772024094743747</v>
+        <v>5.591648341783005</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08635486747054819</v>
+        <v>0.08627258949787525</v>
       </c>
       <c r="C34">
-        <v>1106.528333325688</v>
+        <v>1094.763041202893</v>
       </c>
       <c r="D34">
-        <v>1425.876333325688</v>
+        <v>1428.775041202892</v>
       </c>
       <c r="E34">
-        <v>165.748</v>
+        <v>180.412</v>
       </c>
       <c r="F34">
-        <v>469.248</v>
+        <v>483.912</v>
       </c>
       <c r="G34">
         <v>149.9</v>
@@ -4075,28 +4075,28 @@
         <v>145.1</v>
       </c>
       <c r="M34">
-        <v>25.9494144</v>
+        <v>26.7603336</v>
       </c>
       <c r="N34">
-        <v>119.1505856</v>
+        <v>118.3396664</v>
       </c>
       <c r="O34">
-        <v>21.44710540800001</v>
+        <v>21.301139952</v>
       </c>
       <c r="P34">
-        <v>97.70348019200003</v>
+        <v>97.03852644800003</v>
       </c>
       <c r="Q34">
-        <v>175.503480192</v>
+        <v>174.838526448</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1056531580449238</v>
+        <v>0.1064304619371272</v>
       </c>
       <c r="T34">
-        <v>1.009210230977623</v>
+        <v>1.022316691291741</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.591648341783005</v>
+        <v>5.422204452638065</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08627258949787525</v>
+        <v>0.08619031152520229</v>
       </c>
       <c r="C35">
-        <v>1094.763041202893</v>
+        <v>1083.009558833403</v>
       </c>
       <c r="D35">
-        <v>1428.775041202892</v>
+        <v>1431.685558833403</v>
       </c>
       <c r="E35">
-        <v>180.412</v>
+        <v>195.0760000000001</v>
       </c>
       <c r="F35">
-        <v>483.912</v>
+        <v>498.5760000000001</v>
       </c>
       <c r="G35">
         <v>149.9</v>
@@ -4157,28 +4157,28 @@
         <v>145.1</v>
       </c>
       <c r="M35">
-        <v>26.7603336</v>
+        <v>27.57125280000001</v>
       </c>
       <c r="N35">
-        <v>118.3396664</v>
+        <v>117.5287472</v>
       </c>
       <c r="O35">
-        <v>21.301139952</v>
+        <v>21.155174496</v>
       </c>
       <c r="P35">
-        <v>97.03852644800003</v>
+        <v>96.37357270400001</v>
       </c>
       <c r="Q35">
-        <v>174.838526448</v>
+        <v>174.173572704</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1064304619371272</v>
+        <v>0.1072313204927308</v>
       </c>
       <c r="T35">
-        <v>1.022316691291741</v>
+        <v>1.035820317069923</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.422204452638065</v>
+        <v>5.262727851089886</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08619031152520229</v>
+        <v>0.08610803355252934</v>
       </c>
       <c r="C36">
-        <v>1083.009558833403</v>
+        <v>1071.26795853649</v>
       </c>
       <c r="D36">
-        <v>1431.685558833403</v>
+        <v>1434.60795853649</v>
       </c>
       <c r="E36">
-        <v>195.0760000000001</v>
+        <v>209.7400000000001</v>
       </c>
       <c r="F36">
-        <v>498.5760000000001</v>
+        <v>513.2400000000001</v>
       </c>
       <c r="G36">
         <v>149.9</v>
@@ -4239,28 +4239,28 @@
         <v>145.1</v>
       </c>
       <c r="M36">
-        <v>27.57125280000001</v>
+        <v>28.38217200000001</v>
       </c>
       <c r="N36">
-        <v>117.5287472</v>
+        <v>116.717828</v>
       </c>
       <c r="O36">
-        <v>21.155174496</v>
+        <v>21.00920904</v>
       </c>
       <c r="P36">
-        <v>96.37357270400001</v>
+        <v>95.70861896000001</v>
       </c>
       <c r="Q36">
-        <v>174.173572704</v>
+        <v>173.50861896</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1072313204927308</v>
+        <v>0.1080568208500452</v>
       </c>
       <c r="T36">
-        <v>1.035820317069923</v>
+        <v>1.049739439025895</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.262727851089886</v>
+        <v>5.112364198201603</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08610803355252934</v>
+        <v>0.08602575557985639</v>
       </c>
       <c r="C37">
-        <v>1071.26795853649</v>
+        <v>1059.538313223117</v>
       </c>
       <c r="D37">
-        <v>1434.60795853649</v>
+        <v>1437.542313223117</v>
       </c>
       <c r="E37">
-        <v>209.7400000000001</v>
+        <v>224.4040000000001</v>
       </c>
       <c r="F37">
-        <v>513.2400000000001</v>
+        <v>527.9040000000001</v>
       </c>
       <c r="G37">
         <v>149.9</v>
@@ -4321,28 +4321,28 @@
         <v>145.1</v>
       </c>
       <c r="M37">
-        <v>28.38217200000001</v>
+        <v>29.19309120000001</v>
       </c>
       <c r="N37">
-        <v>116.717828</v>
+        <v>115.9069088</v>
       </c>
       <c r="O37">
-        <v>21.00920904</v>
+        <v>20.863243584</v>
       </c>
       <c r="P37">
-        <v>95.70861896000001</v>
+        <v>95.04366521600001</v>
       </c>
       <c r="Q37">
-        <v>173.50861896</v>
+        <v>172.843665216</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1080568208500452</v>
+        <v>0.1089081180935256</v>
       </c>
       <c r="T37">
-        <v>1.049739439025895</v>
+        <v>1.064093533542992</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.112364198201603</v>
+        <v>4.970354081584892</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08602575557985641</v>
+        <v>0.08594347760718345</v>
       </c>
       <c r="C38">
-        <v>1059.538313223117</v>
+        <v>1047.820696401998</v>
       </c>
       <c r="D38">
-        <v>1437.542313223117</v>
+        <v>1440.488696401998</v>
       </c>
       <c r="E38">
-        <v>224.404</v>
+        <v>239.068</v>
       </c>
       <c r="F38">
-        <v>527.904</v>
+        <v>542.568</v>
       </c>
       <c r="G38">
         <v>149.9</v>
@@ -4403,28 +4403,28 @@
         <v>145.1</v>
       </c>
       <c r="M38">
-        <v>29.1930912</v>
+        <v>30.0040104</v>
       </c>
       <c r="N38">
-        <v>115.9069088</v>
+        <v>115.0959896</v>
       </c>
       <c r="O38">
-        <v>20.863243584</v>
+        <v>20.717278128</v>
       </c>
       <c r="P38">
-        <v>95.04366521600002</v>
+        <v>94.37871147200002</v>
       </c>
       <c r="Q38">
-        <v>172.843665216</v>
+        <v>172.178711472</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1089081180935256</v>
+        <v>0.1097864406463229</v>
       </c>
       <c r="T38">
-        <v>1.064093533542992</v>
+        <v>1.078903313600313</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.970354081584893</v>
+        <v>4.836020187488004</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08594347760718345</v>
+        <v>0.0858611996345105</v>
       </c>
       <c r="C39">
-        <v>1047.820696401998</v>
+        <v>1036.115182185737</v>
       </c>
       <c r="D39">
-        <v>1440.488696401998</v>
+        <v>1443.447182185737</v>
       </c>
       <c r="E39">
-        <v>239.068</v>
+        <v>253.7320000000001</v>
       </c>
       <c r="F39">
-        <v>542.568</v>
+        <v>557.2320000000001</v>
       </c>
       <c r="G39">
         <v>149.9</v>
@@ -4485,28 +4485,28 @@
         <v>145.1</v>
       </c>
       <c r="M39">
-        <v>30.0040104</v>
+        <v>30.81492960000001</v>
       </c>
       <c r="N39">
-        <v>115.0959896</v>
+        <v>114.2850704</v>
       </c>
       <c r="O39">
-        <v>20.717278128</v>
+        <v>20.571312672</v>
       </c>
       <c r="P39">
-        <v>94.37871147200002</v>
+        <v>93.71375772800002</v>
       </c>
       <c r="Q39">
-        <v>172.178711472</v>
+        <v>171.513757728</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1097864406463229</v>
+        <v>0.1106930961846944</v>
       </c>
       <c r="T39">
-        <v>1.078903313600313</v>
+        <v>1.094190828498194</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.836020187488004</v>
+        <v>4.708756498343583</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0858611996345105</v>
+        <v>0.08577892166183756</v>
       </c>
       <c r="C40">
-        <v>1036.115182185737</v>
+        <v>1024.421845297045</v>
       </c>
       <c r="D40">
-        <v>1443.447182185737</v>
+        <v>1446.417845297045</v>
       </c>
       <c r="E40">
-        <v>253.7320000000001</v>
+        <v>268.3960000000001</v>
       </c>
       <c r="F40">
-        <v>557.2320000000001</v>
+        <v>571.8960000000001</v>
       </c>
       <c r="G40">
         <v>149.9</v>
@@ -4567,28 +4567,28 @@
         <v>145.1</v>
       </c>
       <c r="M40">
-        <v>30.81492960000001</v>
+        <v>31.6258488</v>
       </c>
       <c r="N40">
-        <v>114.2850704</v>
+        <v>113.4741512</v>
       </c>
       <c r="O40">
-        <v>20.571312672</v>
+        <v>20.425347216</v>
       </c>
       <c r="P40">
-        <v>93.71375772800002</v>
+        <v>93.04880398400002</v>
       </c>
       <c r="Q40">
-        <v>171.513757728</v>
+        <v>170.848803984</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1106930961846944</v>
+        <v>0.1116294781341599</v>
       </c>
       <c r="T40">
-        <v>1.094190828498194</v>
+        <v>1.109979573392726</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.708756498343583</v>
+        <v>4.588019152232208</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08577892166183756</v>
+        <v>0.0865166436891646</v>
       </c>
       <c r="C41">
-        <v>1024.421845297045</v>
+        <v>983.5510117146765</v>
       </c>
       <c r="D41">
-        <v>1446.417845297045</v>
+        <v>1420.211011714676</v>
       </c>
       <c r="E41">
-        <v>268.3960000000001</v>
+        <v>283.0600000000001</v>
       </c>
       <c r="F41">
-        <v>571.8960000000001</v>
+        <v>586.5600000000001</v>
       </c>
       <c r="G41">
         <v>149.9</v>
@@ -4649,45 +4649,45 @@
         <v>145.1</v>
       </c>
       <c r="M41">
-        <v>31.6258488</v>
+        <v>33.90316800000001</v>
       </c>
       <c r="N41">
-        <v>113.4741512</v>
+        <v>111.196832</v>
       </c>
       <c r="O41">
-        <v>20.425347216</v>
+        <v>20.01542976</v>
       </c>
       <c r="P41">
-        <v>93.04880398400002</v>
+        <v>91.18140224000001</v>
       </c>
       <c r="Q41">
-        <v>170.848803984</v>
+        <v>168.98140224</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1116294781341599</v>
+        <v>0.1125970728152743</v>
       </c>
       <c r="T41">
-        <v>1.109979573392726</v>
+        <v>1.126294609783742</v>
       </c>
       <c r="U41">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V41">
         <v>0.18</v>
       </c>
       <c r="W41">
-        <v>0.045346</v>
+        <v>0.04739600000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.588019152232208</v>
+        <v>4.279836031842216</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0865166436891646</v>
+        <v>0.08645486571649166</v>
       </c>
       <c r="C42">
-        <v>983.5510117146765</v>
+        <v>971.0451238010222</v>
       </c>
       <c r="D42">
-        <v>1420.211011714676</v>
+        <v>1422.369123801022</v>
       </c>
       <c r="E42">
-        <v>283.0600000000001</v>
+        <v>297.724</v>
       </c>
       <c r="F42">
-        <v>586.5600000000001</v>
+        <v>601.224</v>
       </c>
       <c r="G42">
         <v>149.9</v>
@@ -4731,28 +4731,28 @@
         <v>145.1</v>
       </c>
       <c r="M42">
-        <v>33.90316800000001</v>
+        <v>34.75074720000001</v>
       </c>
       <c r="N42">
-        <v>111.196832</v>
+        <v>110.3492528</v>
       </c>
       <c r="O42">
-        <v>20.01542976</v>
+        <v>19.862865504</v>
       </c>
       <c r="P42">
-        <v>91.18140224000001</v>
+        <v>90.48638729600002</v>
       </c>
       <c r="Q42">
-        <v>168.98140224</v>
+        <v>168.286387296</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1125970728152743</v>
+        <v>0.1135974673160876</v>
       </c>
       <c r="T42">
-        <v>1.126294609783742</v>
+        <v>1.14316269825581</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.279836031842216</v>
+        <v>4.175449787163137</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08645486571649166</v>
+        <v>0.08639308774381871</v>
       </c>
       <c r="C43">
-        <v>971.0451238010222</v>
+        <v>958.5458046800818</v>
       </c>
       <c r="D43">
-        <v>1422.369123801022</v>
+        <v>1424.533804680082</v>
       </c>
       <c r="E43">
-        <v>297.724</v>
+        <v>312.3880000000001</v>
       </c>
       <c r="F43">
-        <v>601.224</v>
+        <v>615.8880000000001</v>
       </c>
       <c r="G43">
         <v>149.9</v>
@@ -4813,28 +4813,28 @@
         <v>145.1</v>
       </c>
       <c r="M43">
-        <v>34.75074720000001</v>
+        <v>35.59832640000001</v>
       </c>
       <c r="N43">
-        <v>110.3492528</v>
+        <v>109.5016736</v>
       </c>
       <c r="O43">
-        <v>19.862865504</v>
+        <v>19.710301248</v>
       </c>
       <c r="P43">
-        <v>90.48638729600002</v>
+        <v>89.791372352</v>
       </c>
       <c r="Q43">
-        <v>168.286387296</v>
+        <v>167.591372352</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1135974673160876</v>
+        <v>0.1146323581789978</v>
       </c>
       <c r="T43">
-        <v>1.14316269825581</v>
+        <v>1.160612444951053</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.175449787163137</v>
+        <v>4.076034316040205</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08639308774381872</v>
+        <v>0.08756540977114577</v>
       </c>
       <c r="C44">
-        <v>958.5458046800815</v>
+        <v>903.8962671970465</v>
       </c>
       <c r="D44">
-        <v>1424.533804680081</v>
+        <v>1384.548267197046</v>
       </c>
       <c r="E44">
-        <v>312.388</v>
+        <v>327.052</v>
       </c>
       <c r="F44">
-        <v>615.888</v>
+        <v>630.552</v>
       </c>
       <c r="G44">
         <v>149.9</v>
@@ -4895,45 +4895,45 @@
         <v>145.1</v>
       </c>
       <c r="M44">
-        <v>35.5983264</v>
+        <v>38.6528376</v>
       </c>
       <c r="N44">
-        <v>109.5016736</v>
+        <v>106.4471624</v>
       </c>
       <c r="O44">
-        <v>19.710301248</v>
+        <v>19.160489232</v>
       </c>
       <c r="P44">
-        <v>89.79137235200001</v>
+        <v>87.28667316800002</v>
       </c>
       <c r="Q44">
-        <v>167.591372352</v>
+        <v>165.086673168</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1146323581789978</v>
+        <v>0.1157035610020101</v>
       </c>
       <c r="T44">
-        <v>1.160612444951053</v>
+        <v>1.178674463460164</v>
       </c>
       <c r="U44">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V44">
         <v>0.18</v>
       </c>
       <c r="W44">
-        <v>0.04739600000000001</v>
+        <v>0.05026600000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.076034316040205</v>
+        <v>3.753928793057098</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08756540977114577</v>
+        <v>0.08753233179847282</v>
       </c>
       <c r="C45">
-        <v>903.8962671970465</v>
+        <v>890.3296908916508</v>
       </c>
       <c r="D45">
-        <v>1384.548267197046</v>
+        <v>1385.645690891651</v>
       </c>
       <c r="E45">
-        <v>327.052</v>
+        <v>341.716</v>
       </c>
       <c r="F45">
-        <v>630.552</v>
+        <v>645.216</v>
       </c>
       <c r="G45">
         <v>149.9</v>
@@ -4977,28 +4977,28 @@
         <v>145.1</v>
       </c>
       <c r="M45">
-        <v>38.6528376</v>
+        <v>39.5517408</v>
       </c>
       <c r="N45">
-        <v>106.4471624</v>
+        <v>105.5482592</v>
       </c>
       <c r="O45">
-        <v>19.160489232</v>
+        <v>18.998686656</v>
       </c>
       <c r="P45">
-        <v>87.28667316800002</v>
+        <v>86.54957254400001</v>
       </c>
       <c r="Q45">
-        <v>165.086673168</v>
+        <v>164.349572544</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1157035610020101</v>
+        <v>0.1168130210687015</v>
       </c>
       <c r="T45">
-        <v>1.178674463460164</v>
+        <v>1.197381554058886</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.753928793057098</v>
+        <v>3.668612229578528</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08753233179847282</v>
+        <v>0.08749925382579987</v>
       </c>
       <c r="C46">
-        <v>890.3296908916508</v>
+        <v>876.7648556510292</v>
       </c>
       <c r="D46">
-        <v>1385.645690891651</v>
+        <v>1386.744855651029</v>
       </c>
       <c r="E46">
-        <v>341.716</v>
+        <v>356.3800000000001</v>
       </c>
       <c r="F46">
-        <v>645.216</v>
+        <v>659.8800000000001</v>
       </c>
       <c r="G46">
         <v>149.9</v>
@@ -5059,28 +5059,28 @@
         <v>145.1</v>
       </c>
       <c r="M46">
-        <v>39.5517408</v>
+        <v>40.450644</v>
       </c>
       <c r="N46">
-        <v>105.5482592</v>
+        <v>104.649356</v>
       </c>
       <c r="O46">
-        <v>18.998686656</v>
+        <v>18.83688408</v>
       </c>
       <c r="P46">
-        <v>86.54957254400001</v>
+        <v>85.81247192000001</v>
       </c>
       <c r="Q46">
-        <v>164.349572544</v>
+        <v>163.61247192</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1168130210687015</v>
+        <v>0.1179628251378179</v>
       </c>
       <c r="T46">
-        <v>1.197381554058886</v>
+        <v>1.216768902497562</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.668612229578528</v>
+        <v>3.587087513365671</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08749925382579987</v>
+        <v>0.08746617585312694</v>
       </c>
       <c r="C47">
-        <v>876.7648556510292</v>
+        <v>863.2017656217752</v>
       </c>
       <c r="D47">
-        <v>1386.744855651029</v>
+        <v>1387.845765621775</v>
       </c>
       <c r="E47">
-        <v>356.3800000000001</v>
+        <v>371.0440000000001</v>
       </c>
       <c r="F47">
-        <v>659.8800000000001</v>
+        <v>674.5440000000001</v>
       </c>
       <c r="G47">
         <v>149.9</v>
@@ -5141,28 +5141,28 @@
         <v>145.1</v>
       </c>
       <c r="M47">
-        <v>40.450644</v>
+        <v>41.3495472</v>
       </c>
       <c r="N47">
-        <v>104.649356</v>
+        <v>103.7504528</v>
       </c>
       <c r="O47">
-        <v>18.83688408</v>
+        <v>18.675081504</v>
       </c>
       <c r="P47">
-        <v>85.81247192000001</v>
+        <v>85.07537129600001</v>
       </c>
       <c r="Q47">
-        <v>163.61247192</v>
+        <v>162.875371296</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1179628251378179</v>
+        <v>0.1191552145428276</v>
       </c>
       <c r="T47">
-        <v>1.216768902497562</v>
+        <v>1.23687430087841</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.587087513365671</v>
+        <v>3.509107350031635</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08746617585312694</v>
+        <v>0.08851221788045396</v>
       </c>
       <c r="C48">
-        <v>863.2017656217752</v>
+        <v>814.5487790898305</v>
       </c>
       <c r="D48">
-        <v>1387.845765621775</v>
+        <v>1353.856779089831</v>
       </c>
       <c r="E48">
-        <v>371.0440000000001</v>
+        <v>385.7080000000001</v>
       </c>
       <c r="F48">
-        <v>674.5440000000001</v>
+        <v>689.2080000000001</v>
       </c>
       <c r="G48">
         <v>149.9</v>
@@ -5223,45 +5223,45 @@
         <v>145.1</v>
       </c>
       <c r="M48">
-        <v>41.3495472</v>
+        <v>44.17823280000001</v>
       </c>
       <c r="N48">
-        <v>103.7504528</v>
+        <v>100.9217672</v>
       </c>
       <c r="O48">
-        <v>18.675081504</v>
+        <v>18.165918096</v>
       </c>
       <c r="P48">
-        <v>85.07537129600001</v>
+        <v>82.75584910400001</v>
       </c>
       <c r="Q48">
-        <v>162.875371296</v>
+        <v>160.555849104</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1191552145428276</v>
+        <v>0.1203925997744414</v>
       </c>
       <c r="T48">
-        <v>1.23687430087841</v>
+        <v>1.257738393537782</v>
       </c>
       <c r="U48">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V48">
         <v>0.18</v>
       </c>
       <c r="W48">
-        <v>0.05026600000000001</v>
+        <v>0.052562</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.509107350031635</v>
+        <v>3.284422911547516</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08851221788045396</v>
+        <v>0.08850209990778103</v>
       </c>
       <c r="C49">
-        <v>814.5487790898305</v>
+        <v>800.2055662624396</v>
       </c>
       <c r="D49">
-        <v>1353.856779089831</v>
+        <v>1354.17756626244</v>
       </c>
       <c r="E49">
-        <v>385.7080000000001</v>
+        <v>400.3720000000001</v>
       </c>
       <c r="F49">
-        <v>689.2080000000001</v>
+        <v>703.8720000000001</v>
       </c>
       <c r="G49">
         <v>149.9</v>
@@ -5305,28 +5305,28 @@
         <v>145.1</v>
       </c>
       <c r="M49">
-        <v>44.17823280000001</v>
+        <v>45.11819520000001</v>
       </c>
       <c r="N49">
-        <v>100.9217672</v>
+        <v>99.98180480000002</v>
       </c>
       <c r="O49">
-        <v>18.165918096</v>
+        <v>17.996724864</v>
       </c>
       <c r="P49">
-        <v>82.75584910400001</v>
+        <v>81.98507993600002</v>
       </c>
       <c r="Q49">
-        <v>160.555849104</v>
+        <v>159.785079936</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1203925997744414</v>
+        <v>0.1216775767457327</v>
       </c>
       <c r="T49">
-        <v>1.257738393537782</v>
+        <v>1.279404951299437</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.284422911547516</v>
+        <v>3.21599743422361</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08850209990778102</v>
+        <v>0.08849198193510807</v>
       </c>
       <c r="C50">
-        <v>800.2055662624402</v>
+        <v>785.8625054877632</v>
       </c>
       <c r="D50">
-        <v>1354.17756626244</v>
+        <v>1354.498505487763</v>
       </c>
       <c r="E50">
-        <v>400.3720000000001</v>
+        <v>415.0360000000001</v>
       </c>
       <c r="F50">
-        <v>703.8720000000001</v>
+        <v>718.5360000000001</v>
       </c>
       <c r="G50">
         <v>149.9</v>
@@ -5387,28 +5387,28 @@
         <v>145.1</v>
       </c>
       <c r="M50">
-        <v>45.11819520000001</v>
+        <v>46.05815760000001</v>
       </c>
       <c r="N50">
-        <v>99.98180480000002</v>
+        <v>99.04184240000001</v>
       </c>
       <c r="O50">
-        <v>17.996724864</v>
+        <v>17.827531632</v>
       </c>
       <c r="P50">
-        <v>81.98507993600002</v>
+        <v>81.214310768</v>
       </c>
       <c r="Q50">
-        <v>159.785079936</v>
+        <v>159.014310768</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1216775767457327</v>
+        <v>0.1230129449708001</v>
       </c>
       <c r="T50">
-        <v>1.279404951299437</v>
+        <v>1.301921177992921</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.21599743422361</v>
+        <v>3.150364833525169</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08849198193510807</v>
+        <v>0.08848186396243511</v>
       </c>
       <c r="C51">
-        <v>785.8625054877632</v>
+        <v>771.5195968739351</v>
       </c>
       <c r="D51">
-        <v>1354.498505487763</v>
+        <v>1354.819596873935</v>
       </c>
       <c r="E51">
-        <v>415.0360000000001</v>
+        <v>429.7</v>
       </c>
       <c r="F51">
-        <v>718.5360000000001</v>
+        <v>733.2</v>
       </c>
       <c r="G51">
         <v>149.9</v>
@@ -5469,28 +5469,28 @@
         <v>145.1</v>
       </c>
       <c r="M51">
-        <v>46.05815760000001</v>
+        <v>46.99812000000001</v>
       </c>
       <c r="N51">
-        <v>99.04184240000001</v>
+        <v>98.10188000000002</v>
       </c>
       <c r="O51">
-        <v>17.827531632</v>
+        <v>17.6583384</v>
       </c>
       <c r="P51">
-        <v>81.214310768</v>
+        <v>80.44354160000002</v>
       </c>
       <c r="Q51">
-        <v>159.014310768</v>
+        <v>158.2435416</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1230129449708001</v>
+        <v>0.1244017279248702</v>
       </c>
       <c r="T51">
-        <v>1.301921177992921</v>
+        <v>1.325338053754145</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.150364833525169</v>
+        <v>3.087357536854666</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08848186396243511</v>
+        <v>0.08847174598976218</v>
       </c>
       <c r="C52">
-        <v>771.5195968739351</v>
+        <v>757.1768405291912</v>
       </c>
       <c r="D52">
-        <v>1354.819596873935</v>
+        <v>1355.140840529191</v>
       </c>
       <c r="E52">
-        <v>429.7</v>
+        <v>444.364</v>
       </c>
       <c r="F52">
-        <v>733.2</v>
+        <v>747.864</v>
       </c>
       <c r="G52">
         <v>149.9</v>
@@ -5551,28 +5551,28 @@
         <v>145.1</v>
       </c>
       <c r="M52">
-        <v>46.99812000000001</v>
+        <v>47.93808240000001</v>
       </c>
       <c r="N52">
-        <v>98.10188000000002</v>
+        <v>97.16191760000001</v>
       </c>
       <c r="O52">
-        <v>17.6583384</v>
+        <v>17.489145168</v>
       </c>
       <c r="P52">
-        <v>80.44354160000002</v>
+        <v>79.67277243200002</v>
       </c>
       <c r="Q52">
-        <v>158.2435416</v>
+        <v>157.472772432</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1244017279248702</v>
+        <v>0.1258471958974738</v>
       </c>
       <c r="T52">
-        <v>1.325338053754145</v>
+        <v>1.349710720362766</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.087357536854666</v>
+        <v>3.026821114563398</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08847174598976218</v>
+        <v>0.09178754801708923</v>
       </c>
       <c r="C53">
-        <v>757.1768405291912</v>
+        <v>644.8042446138229</v>
       </c>
       <c r="D53">
-        <v>1355.140840529191</v>
+        <v>1257.432244613823</v>
       </c>
       <c r="E53">
-        <v>444.364</v>
+        <v>459.028</v>
       </c>
       <c r="F53">
-        <v>747.864</v>
+        <v>762.528</v>
       </c>
       <c r="G53">
         <v>149.9</v>
@@ -5633,45 +5633,45 @@
         <v>145.1</v>
       </c>
       <c r="M53">
-        <v>47.93808240000001</v>
+        <v>54.8257632</v>
       </c>
       <c r="N53">
-        <v>97.16191760000001</v>
+        <v>90.27423680000001</v>
       </c>
       <c r="O53">
-        <v>17.489145168</v>
+        <v>16.249362624</v>
       </c>
       <c r="P53">
-        <v>79.67277243200002</v>
+        <v>74.02487417600001</v>
       </c>
       <c r="Q53">
-        <v>157.472772432</v>
+        <v>151.824874176</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1258471958974738</v>
+        <v>0.1273528917022692</v>
       </c>
       <c r="T53">
-        <v>1.349710720362766</v>
+        <v>1.375098914746746</v>
       </c>
       <c r="U53">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V53">
         <v>0.18</v>
       </c>
       <c r="W53">
-        <v>0.052562</v>
+        <v>0.05895800000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.026821114563398</v>
+        <v>2.646565985241041</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09178754801708923</v>
+        <v>0.09184139004441629</v>
       </c>
       <c r="C54">
-        <v>644.8042446138229</v>
+        <v>628.6697698690094</v>
       </c>
       <c r="D54">
-        <v>1257.432244613823</v>
+        <v>1255.961769869009</v>
       </c>
       <c r="E54">
-        <v>459.028</v>
+        <v>473.6920000000001</v>
       </c>
       <c r="F54">
-        <v>762.528</v>
+        <v>777.1920000000001</v>
       </c>
       <c r="G54">
         <v>149.9</v>
@@ -5715,28 +5715,28 @@
         <v>145.1</v>
       </c>
       <c r="M54">
-        <v>54.8257632</v>
+        <v>55.88010480000001</v>
       </c>
       <c r="N54">
-        <v>90.27423680000001</v>
+        <v>89.21989520000001</v>
       </c>
       <c r="O54">
-        <v>16.249362624</v>
+        <v>16.059581136</v>
       </c>
       <c r="P54">
-        <v>74.02487417600001</v>
+        <v>73.160314064</v>
       </c>
       <c r="Q54">
-        <v>151.824874176</v>
+        <v>150.960314064</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1273528917022692</v>
+        <v>0.1289226596689708</v>
       </c>
       <c r="T54">
-        <v>1.375098914746746</v>
+        <v>1.401567457827916</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.646565985241041</v>
+        <v>2.596630777972342</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09184139004441629</v>
+        <v>0.09189523207174333</v>
       </c>
       <c r="C55">
-        <v>628.6697698690094</v>
+        <v>612.5387303316066</v>
       </c>
       <c r="D55">
-        <v>1255.961769869009</v>
+        <v>1254.494730331607</v>
       </c>
       <c r="E55">
-        <v>473.6920000000001</v>
+        <v>488.3560000000001</v>
       </c>
       <c r="F55">
-        <v>777.1920000000001</v>
+        <v>791.8560000000001</v>
       </c>
       <c r="G55">
         <v>149.9</v>
@@ -5797,28 +5797,28 @@
         <v>145.1</v>
       </c>
       <c r="M55">
-        <v>55.88010480000001</v>
+        <v>56.93444640000001</v>
       </c>
       <c r="N55">
-        <v>89.21989520000001</v>
+        <v>88.16555360000001</v>
       </c>
       <c r="O55">
-        <v>16.059581136</v>
+        <v>15.869799648</v>
       </c>
       <c r="P55">
-        <v>73.160314064</v>
+        <v>72.29575395200001</v>
       </c>
       <c r="Q55">
-        <v>150.960314064</v>
+        <v>150.095753952</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1289226596689708</v>
+        <v>0.1305606784168333</v>
       </c>
       <c r="T55">
-        <v>1.401567457827916</v>
+        <v>1.429186807130007</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.596630777972342</v>
+        <v>2.548545022824706</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09189523207174333</v>
+        <v>0.09194907409907038</v>
       </c>
       <c r="C56">
-        <v>612.5387303316066</v>
+        <v>596.4111139780658</v>
       </c>
       <c r="D56">
-        <v>1254.494730331607</v>
+        <v>1253.031113978066</v>
       </c>
       <c r="E56">
-        <v>488.3560000000001</v>
+        <v>503.0200000000001</v>
       </c>
       <c r="F56">
-        <v>791.8560000000001</v>
+        <v>806.5200000000001</v>
       </c>
       <c r="G56">
         <v>149.9</v>
@@ -5879,28 +5879,28 @@
         <v>145.1</v>
       </c>
       <c r="M56">
-        <v>56.93444640000001</v>
+        <v>57.98878800000001</v>
       </c>
       <c r="N56">
-        <v>88.16555360000001</v>
+        <v>87.11121200000001</v>
       </c>
       <c r="O56">
-        <v>15.869799648</v>
+        <v>15.68001816</v>
       </c>
       <c r="P56">
-        <v>72.29575395200001</v>
+        <v>71.43119384000001</v>
       </c>
       <c r="Q56">
-        <v>150.095753952</v>
+        <v>149.23119384</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1305606784168333</v>
+        <v>0.1322714979979342</v>
       </c>
       <c r="T56">
-        <v>1.429186807130007</v>
+        <v>1.458033683067747</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.548545022824706</v>
+        <v>2.502207840591529</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09194907409907038</v>
+        <v>0.09379379612639743</v>
       </c>
       <c r="C57">
-        <v>596.4111139780658</v>
+        <v>533.5847621025465</v>
       </c>
       <c r="D57">
-        <v>1253.031113978066</v>
+        <v>1204.868762102546</v>
       </c>
       <c r="E57">
-        <v>503.0200000000001</v>
+        <v>517.6840000000001</v>
       </c>
       <c r="F57">
-        <v>806.5200000000001</v>
+        <v>821.1840000000001</v>
       </c>
       <c r="G57">
         <v>149.9</v>
@@ -5961,45 +5961,45 @@
         <v>145.1</v>
       </c>
       <c r="M57">
-        <v>57.98878800000001</v>
+        <v>62.24574720000001</v>
       </c>
       <c r="N57">
-        <v>87.11121200000001</v>
+        <v>82.85425280000001</v>
       </c>
       <c r="O57">
-        <v>15.68001816</v>
+        <v>14.913765504</v>
       </c>
       <c r="P57">
-        <v>71.43119384000001</v>
+        <v>67.94048729600001</v>
       </c>
       <c r="Q57">
-        <v>149.23119384</v>
+        <v>145.740487296</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1322714979979342</v>
+        <v>0.1340600821054487</v>
       </c>
       <c r="T57">
-        <v>1.458033683067747</v>
+        <v>1.48819178063902</v>
       </c>
       <c r="U57">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V57">
         <v>0.18</v>
       </c>
       <c r="W57">
-        <v>0.05895800000000001</v>
+        <v>0.06215600000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.502207840591529</v>
+        <v>2.331082949872598</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09379379612639743</v>
+        <v>0.09387961815372448</v>
       </c>
       <c r="C58">
-        <v>533.5847621025465</v>
+        <v>516.7700736445797</v>
       </c>
       <c r="D58">
-        <v>1204.868762102546</v>
+        <v>1202.71807364458</v>
       </c>
       <c r="E58">
-        <v>517.6840000000001</v>
+        <v>532.3480000000002</v>
       </c>
       <c r="F58">
-        <v>821.1840000000001</v>
+        <v>835.8480000000002</v>
       </c>
       <c r="G58">
         <v>149.9</v>
@@ -6043,28 +6043,28 @@
         <v>145.1</v>
       </c>
       <c r="M58">
-        <v>62.24574720000001</v>
+        <v>63.35727840000002</v>
       </c>
       <c r="N58">
-        <v>82.85425280000001</v>
+        <v>81.74272160000001</v>
       </c>
       <c r="O58">
-        <v>14.913765504</v>
+        <v>14.713689888</v>
       </c>
       <c r="P58">
-        <v>67.94048729600001</v>
+        <v>67.02903171200001</v>
       </c>
       <c r="Q58">
-        <v>145.740487296</v>
+        <v>144.829031712</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1340600821054487</v>
+        <v>0.1359318561714523</v>
       </c>
       <c r="T58">
-        <v>1.48819178063902</v>
+        <v>1.519752580422911</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.331082949872598</v>
+        <v>2.29018675776957</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09387961815372448</v>
+        <v>0.09396544018105155</v>
       </c>
       <c r="C59">
-        <v>516.7700736445797</v>
+        <v>499.9630494555536</v>
       </c>
       <c r="D59">
-        <v>1202.71807364458</v>
+        <v>1200.575049455554</v>
       </c>
       <c r="E59">
-        <v>532.3480000000002</v>
+        <v>547.0120000000002</v>
       </c>
       <c r="F59">
-        <v>835.8480000000002</v>
+        <v>850.5120000000002</v>
       </c>
       <c r="G59">
         <v>149.9</v>
@@ -6125,28 +6125,28 @@
         <v>145.1</v>
       </c>
       <c r="M59">
-        <v>63.35727840000002</v>
+        <v>64.46880960000001</v>
       </c>
       <c r="N59">
-        <v>81.74272160000001</v>
+        <v>80.63119040000001</v>
       </c>
       <c r="O59">
-        <v>14.713689888</v>
+        <v>14.513614272</v>
       </c>
       <c r="P59">
-        <v>67.02903171200001</v>
+        <v>66.11757612800001</v>
       </c>
       <c r="Q59">
-        <v>144.829031712</v>
+        <v>143.917576128</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1359318561714523</v>
+        <v>0.137892762335837</v>
       </c>
       <c r="T59">
-        <v>1.519752580422911</v>
+        <v>1.552816275434606</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.29018675776957</v>
+        <v>2.250700779187336</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09396544018105155</v>
+        <v>0.09405126220837859</v>
       </c>
       <c r="C60">
-        <v>499.9630494555538</v>
+        <v>483.1636486393519</v>
       </c>
       <c r="D60">
-        <v>1200.575049455554</v>
+        <v>1198.439648639352</v>
       </c>
       <c r="E60">
-        <v>547.0119999999999</v>
+        <v>561.676</v>
       </c>
       <c r="F60">
-        <v>850.5119999999999</v>
+        <v>865.176</v>
       </c>
       <c r="G60">
         <v>149.9</v>
@@ -6207,28 +6207,28 @@
         <v>145.1</v>
       </c>
       <c r="M60">
-        <v>64.4688096</v>
+        <v>65.5803408</v>
       </c>
       <c r="N60">
-        <v>80.63119040000002</v>
+        <v>79.51965920000002</v>
       </c>
       <c r="O60">
-        <v>14.513614272</v>
+        <v>14.313538656</v>
       </c>
       <c r="P60">
-        <v>66.11757612800002</v>
+        <v>65.20612054400002</v>
       </c>
       <c r="Q60">
-        <v>143.917576128</v>
+        <v>143.006120544</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.137892762335837</v>
+        <v>0.1399493224594599</v>
       </c>
       <c r="T60">
-        <v>1.552816275434605</v>
+        <v>1.587492833617602</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.250700779187336</v>
+        <v>2.212553308353653</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09405126220837859</v>
+        <v>0.09413708423570563</v>
       </c>
       <c r="C61">
-        <v>483.1636486393519</v>
+        <v>466.3718305902986</v>
       </c>
       <c r="D61">
-        <v>1198.439648639352</v>
+        <v>1196.311830590299</v>
       </c>
       <c r="E61">
-        <v>561.676</v>
+        <v>576.34</v>
       </c>
       <c r="F61">
-        <v>865.176</v>
+        <v>879.84</v>
       </c>
       <c r="G61">
         <v>149.9</v>
@@ -6289,28 +6289,28 @@
         <v>145.1</v>
       </c>
       <c r="M61">
-        <v>65.5803408</v>
+        <v>66.691872</v>
       </c>
       <c r="N61">
-        <v>79.51965920000002</v>
+        <v>78.40812800000002</v>
       </c>
       <c r="O61">
-        <v>14.313538656</v>
+        <v>14.11346304</v>
       </c>
       <c r="P61">
-        <v>65.20612054400002</v>
+        <v>64.29466496000002</v>
       </c>
       <c r="Q61">
-        <v>143.006120544</v>
+        <v>142.09466496</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1399493224594599</v>
+        <v>0.1421087105892641</v>
       </c>
       <c r="T61">
-        <v>1.587492833617602</v>
+        <v>1.623903219709749</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.212553308353653</v>
+        <v>2.175677419881092</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09413708423570563</v>
+        <v>0.0942229062630327</v>
       </c>
       <c r="C62">
-        <v>466.3718305902986</v>
+        <v>449.5875549905874</v>
       </c>
       <c r="D62">
-        <v>1196.311830590299</v>
+        <v>1194.191554990587</v>
       </c>
       <c r="E62">
-        <v>576.34</v>
+        <v>591.004</v>
       </c>
       <c r="F62">
-        <v>879.84</v>
+        <v>894.504</v>
       </c>
       <c r="G62">
         <v>149.9</v>
@@ -6371,28 +6371,28 @@
         <v>145.1</v>
       </c>
       <c r="M62">
-        <v>66.691872</v>
+        <v>67.80340320000001</v>
       </c>
       <c r="N62">
-        <v>78.40812800000002</v>
+        <v>77.29659680000002</v>
       </c>
       <c r="O62">
-        <v>14.11346304</v>
+        <v>13.913387424</v>
       </c>
       <c r="P62">
-        <v>64.29466496000002</v>
+        <v>63.38320937600001</v>
       </c>
       <c r="Q62">
-        <v>142.09466496</v>
+        <v>141.183209376</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1421087105892641</v>
+        <v>0.1443788365718787</v>
       </c>
       <c r="T62">
-        <v>1.623903219709749</v>
+        <v>1.662180805088673</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.175677419881092</v>
+        <v>2.140010576932221</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.0942229062630327</v>
+        <v>0.09430872829035974</v>
       </c>
       <c r="C63">
-        <v>449.5875549905874</v>
+        <v>432.8107818077355</v>
       </c>
       <c r="D63">
-        <v>1194.191554990587</v>
+        <v>1192.078781807735</v>
       </c>
       <c r="E63">
-        <v>591.004</v>
+        <v>605.668</v>
       </c>
       <c r="F63">
-        <v>894.504</v>
+        <v>909.168</v>
       </c>
       <c r="G63">
         <v>149.9</v>
@@ -6453,28 +6453,28 @@
         <v>145.1</v>
       </c>
       <c r="M63">
-        <v>67.80340320000001</v>
+        <v>68.91493440000001</v>
       </c>
       <c r="N63">
-        <v>77.29659680000002</v>
+        <v>76.18506560000002</v>
       </c>
       <c r="O63">
-        <v>13.913387424</v>
+        <v>13.713311808</v>
       </c>
       <c r="P63">
-        <v>63.38320937600001</v>
+        <v>62.47175379200002</v>
       </c>
       <c r="Q63">
-        <v>141.183209376</v>
+        <v>140.271753792</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1443788365718787</v>
+        <v>0.1467684428693677</v>
       </c>
       <c r="T63">
-        <v>1.662180805088673</v>
+        <v>1.702473000224382</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.140010576932221</v>
+        <v>2.105494277304282</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09430872829035974</v>
+        <v>0.09439455031768679</v>
       </c>
       <c r="C64">
-        <v>432.8107818077355</v>
+        <v>416.0414712920608</v>
       </c>
       <c r="D64">
-        <v>1192.078781807735</v>
+        <v>1189.973471292061</v>
       </c>
       <c r="E64">
-        <v>605.668</v>
+        <v>620.3320000000001</v>
       </c>
       <c r="F64">
-        <v>909.168</v>
+        <v>923.8320000000001</v>
       </c>
       <c r="G64">
         <v>149.9</v>
@@ -6535,28 +6535,28 @@
         <v>145.1</v>
       </c>
       <c r="M64">
-        <v>68.91493440000001</v>
+        <v>70.02646560000001</v>
       </c>
       <c r="N64">
-        <v>76.18506560000002</v>
+        <v>75.07353440000001</v>
       </c>
       <c r="O64">
-        <v>13.713311808</v>
+        <v>13.513236192</v>
       </c>
       <c r="P64">
-        <v>62.47175379200002</v>
+        <v>61.56029820800001</v>
       </c>
       <c r="Q64">
-        <v>140.271753792</v>
+        <v>139.360298208</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1467684428693677</v>
+        <v>0.1492872170748292</v>
       </c>
       <c r="T64">
-        <v>1.702473000224382</v>
+        <v>1.744943151853913</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.105494277304282</v>
+        <v>2.072073733220087</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09439455031768679</v>
+        <v>0.09448037234501386</v>
       </c>
       <c r="C65">
-        <v>416.0414712920608</v>
+        <v>399.2795839741925</v>
       </c>
       <c r="D65">
-        <v>1189.973471292061</v>
+        <v>1187.875583974193</v>
       </c>
       <c r="E65">
-        <v>620.3320000000001</v>
+        <v>634.9960000000001</v>
       </c>
       <c r="F65">
-        <v>923.8320000000001</v>
+        <v>938.4960000000001</v>
       </c>
       <c r="G65">
         <v>149.9</v>
@@ -6617,28 +6617,28 @@
         <v>145.1</v>
       </c>
       <c r="M65">
-        <v>70.02646560000001</v>
+        <v>71.13799680000001</v>
       </c>
       <c r="N65">
-        <v>75.07353440000001</v>
+        <v>73.96200320000001</v>
       </c>
       <c r="O65">
-        <v>13.513236192</v>
+        <v>13.313160576</v>
       </c>
       <c r="P65">
-        <v>61.56029820800001</v>
+        <v>60.64884262400001</v>
       </c>
       <c r="Q65">
-        <v>139.360298208</v>
+        <v>138.448842624</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1492872170748292</v>
+        <v>0.151945923180594</v>
       </c>
       <c r="T65">
-        <v>1.744943151853913</v>
+        <v>1.789772756351752</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.072073733220087</v>
+        <v>2.039697581138523</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09448037234501386</v>
+        <v>0.0945661943723409</v>
       </c>
       <c r="C66">
-        <v>399.2795839741925</v>
+        <v>382.5250806626038</v>
       </c>
       <c r="D66">
-        <v>1187.875583974193</v>
+        <v>1185.785080662604</v>
       </c>
       <c r="E66">
-        <v>634.9960000000001</v>
+        <v>649.6600000000001</v>
       </c>
       <c r="F66">
-        <v>938.4960000000001</v>
+        <v>953.1600000000001</v>
       </c>
       <c r="G66">
         <v>149.9</v>
@@ -6699,28 +6699,28 @@
         <v>145.1</v>
       </c>
       <c r="M66">
-        <v>71.13799680000001</v>
+        <v>72.24952800000001</v>
       </c>
       <c r="N66">
-        <v>73.96200320000001</v>
+        <v>72.85047200000001</v>
       </c>
       <c r="O66">
-        <v>13.313160576</v>
+        <v>13.11308496</v>
       </c>
       <c r="P66">
-        <v>60.64884262400001</v>
+        <v>59.73738704000001</v>
       </c>
       <c r="Q66">
-        <v>138.448842624</v>
+        <v>137.53738704</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.151945923180594</v>
+        <v>0.1547565553495454</v>
       </c>
       <c r="T66">
-        <v>1.789772756351752</v>
+        <v>1.837164052535181</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.039697581138523</v>
+        <v>2.008317618351777</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0945661943723409</v>
+        <v>0.1023370563996679</v>
       </c>
       <c r="C67">
-        <v>382.5250806626038</v>
+        <v>204.8782010667342</v>
       </c>
       <c r="D67">
-        <v>1185.785080662604</v>
+        <v>1022.802201066734</v>
       </c>
       <c r="E67">
-        <v>649.6600000000001</v>
+        <v>664.3240000000001</v>
       </c>
       <c r="F67">
-        <v>953.1600000000001</v>
+        <v>967.8240000000001</v>
       </c>
       <c r="G67">
         <v>149.9</v>
@@ -6781,45 +6781,45 @@
         <v>145.1</v>
       </c>
       <c r="M67">
-        <v>72.24952800000001</v>
+        <v>87.10416000000001</v>
       </c>
       <c r="N67">
-        <v>72.85047200000001</v>
+        <v>57.99584000000002</v>
       </c>
       <c r="O67">
-        <v>13.11308496</v>
+        <v>10.4392512</v>
       </c>
       <c r="P67">
-        <v>59.73738704000001</v>
+        <v>47.55658880000001</v>
       </c>
       <c r="Q67">
-        <v>137.53738704</v>
+        <v>125.3565888</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1547565553495454</v>
+        <v>0.1577325188225528</v>
       </c>
       <c r="T67">
-        <v>1.837164052535181</v>
+        <v>1.887343072023517</v>
       </c>
       <c r="U67">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V67">
         <v>0.18</v>
       </c>
       <c r="W67">
-        <v>0.06215600000000001</v>
+        <v>0.0738</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.008317618351777</v>
+        <v>1.665821701282694</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1023370563996679</v>
+        <v>0.102539318426995</v>
       </c>
       <c r="C68">
-        <v>204.8782010667342</v>
+        <v>186.5681571508472</v>
       </c>
       <c r="D68">
-        <v>1022.802201066734</v>
+        <v>1019.156157150847</v>
       </c>
       <c r="E68">
-        <v>664.3240000000001</v>
+        <v>678.9880000000002</v>
       </c>
       <c r="F68">
-        <v>967.8240000000001</v>
+        <v>982.4880000000002</v>
       </c>
       <c r="G68">
         <v>149.9</v>
@@ -6863,28 +6863,28 @@
         <v>145.1</v>
       </c>
       <c r="M68">
-        <v>87.10416000000001</v>
+        <v>88.42392000000001</v>
       </c>
       <c r="N68">
-        <v>57.99584000000002</v>
+        <v>56.67608000000001</v>
       </c>
       <c r="O68">
-        <v>10.4392512</v>
+        <v>10.2016944</v>
       </c>
       <c r="P68">
-        <v>47.55658880000001</v>
+        <v>46.47438560000001</v>
       </c>
       <c r="Q68">
-        <v>125.3565888</v>
+        <v>124.2743856</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1577325188225528</v>
+        <v>0.1608888437181666</v>
       </c>
       <c r="T68">
-        <v>1.887343072023517</v>
+        <v>1.940563244208117</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.665821701282694</v>
+        <v>1.640958690815788</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.102539318426995</v>
+        <v>0.1027415804543221</v>
       </c>
       <c r="C69">
-        <v>186.5681571508472</v>
+        <v>168.2840154395795</v>
       </c>
       <c r="D69">
-        <v>1019.156157150847</v>
+        <v>1015.53601543958</v>
       </c>
       <c r="E69">
-        <v>678.9880000000002</v>
+        <v>693.6520000000002</v>
       </c>
       <c r="F69">
-        <v>982.4880000000002</v>
+        <v>997.1520000000002</v>
       </c>
       <c r="G69">
         <v>149.9</v>
@@ -6945,28 +6945,28 @@
         <v>145.1</v>
       </c>
       <c r="M69">
-        <v>88.42392000000001</v>
+        <v>89.74368000000001</v>
       </c>
       <c r="N69">
-        <v>56.67608000000001</v>
+        <v>55.35632000000001</v>
       </c>
       <c r="O69">
-        <v>10.2016944</v>
+        <v>9.964137600000001</v>
       </c>
       <c r="P69">
-        <v>46.47438560000001</v>
+        <v>45.39218240000001</v>
       </c>
       <c r="Q69">
-        <v>124.2743856</v>
+        <v>123.1921824</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1608888437181666</v>
+        <v>0.1642424389197564</v>
       </c>
       <c r="T69">
-        <v>1.940563244208117</v>
+        <v>1.997109677154255</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.640958690815788</v>
+        <v>1.616826945362615</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1027415804543221</v>
+        <v>0.1029438424816491</v>
       </c>
       <c r="C70">
-        <v>168.2840154395795</v>
+        <v>150.0255008884727</v>
       </c>
       <c r="D70">
-        <v>1015.53601543958</v>
+        <v>1011.941500888473</v>
       </c>
       <c r="E70">
-        <v>693.6520000000002</v>
+        <v>708.3160000000001</v>
       </c>
       <c r="F70">
-        <v>997.1520000000002</v>
+        <v>1011.816</v>
       </c>
       <c r="G70">
         <v>149.9</v>
@@ -7027,28 +7027,28 @@
         <v>145.1</v>
       </c>
       <c r="M70">
-        <v>89.74368000000001</v>
+        <v>91.06344000000001</v>
       </c>
       <c r="N70">
-        <v>55.35632000000001</v>
+        <v>54.03656000000001</v>
       </c>
       <c r="O70">
-        <v>9.964137600000001</v>
+        <v>9.726580800000001</v>
       </c>
       <c r="P70">
-        <v>45.39218240000001</v>
+        <v>44.30997920000001</v>
       </c>
       <c r="Q70">
-        <v>123.1921824</v>
+        <v>122.1099792</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1642424389197564</v>
+        <v>0.1678123951020939</v>
       </c>
       <c r="T70">
-        <v>1.997109677154255</v>
+        <v>2.057304267064659</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.616826945362615</v>
+        <v>1.593394670792142</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1029438424816491</v>
+        <v>0.1031461045089762</v>
       </c>
       <c r="C71">
-        <v>150.0255008884727</v>
+        <v>131.7923423334387</v>
       </c>
       <c r="D71">
-        <v>1011.941500888473</v>
+        <v>1008.372342333439</v>
       </c>
       <c r="E71">
-        <v>708.3160000000001</v>
+        <v>722.9800000000002</v>
       </c>
       <c r="F71">
-        <v>1011.816</v>
+        <v>1026.48</v>
       </c>
       <c r="G71">
         <v>149.9</v>
@@ -7109,28 +7109,28 @@
         <v>145.1</v>
       </c>
       <c r="M71">
-        <v>91.06344000000001</v>
+        <v>92.38320000000002</v>
       </c>
       <c r="N71">
-        <v>54.03656000000001</v>
+        <v>52.71680000000001</v>
       </c>
       <c r="O71">
-        <v>9.726580800000001</v>
+        <v>9.489024000000001</v>
       </c>
       <c r="P71">
-        <v>44.30997920000001</v>
+        <v>43.22777600000001</v>
       </c>
       <c r="Q71">
-        <v>122.1099792</v>
+        <v>121.027776</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1678123951020939</v>
+        <v>0.1716203483632538</v>
       </c>
       <c r="T71">
-        <v>2.057304267064659</v>
+        <v>2.121511829635756</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.593394670792142</v>
+        <v>1.570631889780826</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1031461045089762</v>
+        <v>0.1033483665363032</v>
       </c>
       <c r="C72">
-        <v>131.7923423334387</v>
+        <v>113.5842724225713</v>
       </c>
       <c r="D72">
-        <v>1008.372342333439</v>
+        <v>1004.828272422571</v>
       </c>
       <c r="E72">
-        <v>722.9800000000002</v>
+        <v>737.6440000000002</v>
       </c>
       <c r="F72">
-        <v>1026.48</v>
+        <v>1041.144</v>
       </c>
       <c r="G72">
         <v>149.9</v>
@@ -7191,28 +7191,28 @@
         <v>145.1</v>
       </c>
       <c r="M72">
-        <v>92.38320000000002</v>
+        <v>93.70296000000002</v>
       </c>
       <c r="N72">
-        <v>52.71680000000001</v>
+        <v>51.39704</v>
       </c>
       <c r="O72">
-        <v>9.489024000000001</v>
+        <v>9.2514672</v>
       </c>
       <c r="P72">
-        <v>43.22777600000001</v>
+        <v>42.1455728</v>
       </c>
       <c r="Q72">
-        <v>121.027776</v>
+        <v>119.9455728</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1716203483632538</v>
+        <v>0.1756909190907007</v>
       </c>
       <c r="T72">
-        <v>2.121511829635756</v>
+        <v>2.190147499970378</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.570631889780826</v>
+        <v>1.54851031386842</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1033483665363032</v>
+        <v>0.1035506285636303</v>
       </c>
       <c r="C73">
-        <v>113.5842724225715</v>
+        <v>95.40102754938698</v>
       </c>
       <c r="D73">
-        <v>1004.828272422571</v>
+        <v>1001.309027549387</v>
       </c>
       <c r="E73">
-        <v>737.644</v>
+        <v>752.308</v>
       </c>
       <c r="F73">
-        <v>1041.144</v>
+        <v>1055.808</v>
       </c>
       <c r="G73">
         <v>149.9</v>
@@ -7273,28 +7273,28 @@
         <v>145.1</v>
       </c>
       <c r="M73">
-        <v>93.70295999999999</v>
+        <v>95.02271999999999</v>
       </c>
       <c r="N73">
-        <v>51.39704000000003</v>
+        <v>50.07728000000003</v>
       </c>
       <c r="O73">
-        <v>9.251467200000006</v>
+        <v>9.013910400000006</v>
       </c>
       <c r="P73">
-        <v>42.14557280000002</v>
+        <v>41.06336960000002</v>
       </c>
       <c r="Q73">
-        <v>119.9455728</v>
+        <v>118.8633696</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1756909190907007</v>
+        <v>0.180052244870108</v>
       </c>
       <c r="T73">
-        <v>2.190147499970378</v>
+        <v>2.263685718186044</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.54851031386842</v>
+        <v>1.527003226175804</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1035506285636303</v>
+        <v>0.1037528905909573</v>
       </c>
       <c r="C74">
-        <v>95.40102754938698</v>
+        <v>77.24234778746654</v>
       </c>
       <c r="D74">
-        <v>1001.309027549387</v>
+        <v>997.8143477874664</v>
       </c>
       <c r="E74">
-        <v>752.308</v>
+        <v>766.972</v>
       </c>
       <c r="F74">
-        <v>1055.808</v>
+        <v>1070.472</v>
       </c>
       <c r="G74">
         <v>149.9</v>
@@ -7355,28 +7355,28 @@
         <v>145.1</v>
       </c>
       <c r="M74">
-        <v>95.02271999999999</v>
+        <v>96.34247999999999</v>
       </c>
       <c r="N74">
-        <v>50.07728000000003</v>
+        <v>48.75752000000003</v>
       </c>
       <c r="O74">
-        <v>9.013910400000006</v>
+        <v>8.776353600000006</v>
       </c>
       <c r="P74">
-        <v>41.06336960000002</v>
+        <v>39.98116640000002</v>
       </c>
       <c r="Q74">
-        <v>118.8633696</v>
+        <v>117.7811664</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.180052244870108</v>
+        <v>0.1847366318183604</v>
       </c>
       <c r="T74">
-        <v>2.263685718186044</v>
+        <v>2.342671211825092</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.527003226175804</v>
+        <v>1.506085373762436</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1037528905909573</v>
+        <v>0.1406769076250935</v>
       </c>
       <c r="C75">
-        <v>77.24234778746654</v>
+        <v>-325.7491693803191</v>
       </c>
       <c r="D75">
-        <v>997.8143477874664</v>
+        <v>609.4868306196809</v>
       </c>
       <c r="E75">
-        <v>766.972</v>
+        <v>781.636</v>
       </c>
       <c r="F75">
-        <v>1070.472</v>
+        <v>1085.136</v>
       </c>
       <c r="G75">
         <v>149.9</v>
@@ -7437,45 +7437,45 @@
         <v>145.1</v>
       </c>
       <c r="M75">
-        <v>96.34247999999999</v>
+        <v>159.2979648</v>
       </c>
       <c r="N75">
-        <v>48.75752000000003</v>
+        <v>-14.19796479999999</v>
       </c>
       <c r="O75">
-        <v>8.776353600000006</v>
+        <v>-2.555633663999999</v>
       </c>
       <c r="P75">
-        <v>39.98116640000002</v>
+        <v>-11.642331136</v>
       </c>
       <c r="Q75">
-        <v>117.7811664</v>
+        <v>66.157668864</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1847366318183604</v>
+        <v>0.1917533586738772</v>
       </c>
       <c r="T75">
-        <v>2.342671211825092</v>
+        <v>2.46098330699053</v>
       </c>
       <c r="U75">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.18</v>
+        <v>0.1639568969559114</v>
       </c>
       <c r="W75">
-        <v>0.0738</v>
+        <v>0.1227311275268722</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>1.506085373762436</v>
+        <v>0.9108716497550633</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1406769076250935</v>
+        <v>0.1416869076250935</v>
       </c>
       <c r="C76">
-        <v>-325.7491693803191</v>
+        <v>-346.833041646226</v>
       </c>
       <c r="D76">
-        <v>609.4868306196809</v>
+        <v>603.0669583537742</v>
       </c>
       <c r="E76">
-        <v>781.636</v>
+        <v>796.3000000000002</v>
       </c>
       <c r="F76">
-        <v>1085.136</v>
+        <v>1099.8</v>
       </c>
       <c r="G76">
         <v>149.9</v>
@@ -7519,37 +7519,37 @@
         <v>145.1</v>
       </c>
       <c r="M76">
-        <v>159.2979648</v>
+        <v>161.45064</v>
       </c>
       <c r="N76">
-        <v>-14.19796479999999</v>
+        <v>-16.35064000000003</v>
       </c>
       <c r="O76">
-        <v>-2.555633663999999</v>
+        <v>-2.943115200000005</v>
       </c>
       <c r="P76">
-        <v>-11.642331136</v>
+        <v>-13.40752480000002</v>
       </c>
       <c r="Q76">
-        <v>66.157668864</v>
+        <v>64.39247519999998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1917533586738772</v>
+        <v>0.1975914930208323</v>
       </c>
       <c r="T76">
-        <v>2.46098330699053</v>
+        <v>2.559422639270152</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1639568969559114</v>
+        <v>0.1617708049964992</v>
       </c>
       <c r="W76">
-        <v>0.1227311275268722</v>
+        <v>0.1230520458265139</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.9108716497550633</v>
+        <v>0.8987266944249956</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1416869076250935</v>
+        <v>0.1426969076250935</v>
       </c>
       <c r="C77">
-        <v>-346.833041646226</v>
+        <v>-367.7830794865046</v>
       </c>
       <c r="D77">
-        <v>603.0669583537742</v>
+        <v>596.7809205134956</v>
       </c>
       <c r="E77">
-        <v>796.3000000000002</v>
+        <v>810.9640000000002</v>
       </c>
       <c r="F77">
-        <v>1099.8</v>
+        <v>1114.464</v>
       </c>
       <c r="G77">
         <v>149.9</v>
@@ -7601,37 +7601,37 @@
         <v>145.1</v>
       </c>
       <c r="M77">
-        <v>161.45064</v>
+        <v>163.6033152000001</v>
       </c>
       <c r="N77">
-        <v>-16.35064000000003</v>
+        <v>-18.50331520000003</v>
       </c>
       <c r="O77">
-        <v>-2.943115200000005</v>
+        <v>-3.330596736000006</v>
       </c>
       <c r="P77">
-        <v>-13.40752480000002</v>
+        <v>-15.17271846400003</v>
       </c>
       <c r="Q77">
-        <v>64.39247519999998</v>
+        <v>62.62728153599997</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1975914930208323</v>
+        <v>0.203916138563367</v>
       </c>
       <c r="T77">
-        <v>2.559422639270152</v>
+        <v>2.666065249239741</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1617708049964992</v>
+        <v>0.159642241772861</v>
       </c>
       <c r="W77">
-        <v>0.1230520458265139</v>
+        <v>0.123364518907744</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8987266944249956</v>
+        <v>0.8869013431825614</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1426969076250935</v>
+        <v>0.1437069076250935</v>
       </c>
       <c r="C78">
-        <v>-367.7830794865046</v>
+        <v>-388.6034247775508</v>
       </c>
       <c r="D78">
-        <v>596.7809205134956</v>
+        <v>590.6245752224494</v>
       </c>
       <c r="E78">
-        <v>810.9640000000002</v>
+        <v>825.6280000000002</v>
       </c>
       <c r="F78">
-        <v>1114.464</v>
+        <v>1129.128</v>
       </c>
       <c r="G78">
         <v>149.9</v>
@@ -7683,37 +7683,37 @@
         <v>145.1</v>
       </c>
       <c r="M78">
-        <v>163.6033152000001</v>
+        <v>165.7559904</v>
       </c>
       <c r="N78">
-        <v>-18.50331520000003</v>
+        <v>-20.65599040000001</v>
       </c>
       <c r="O78">
-        <v>-3.330596736000006</v>
+        <v>-3.718078272000001</v>
       </c>
       <c r="P78">
-        <v>-15.17271846400003</v>
+        <v>-16.93791212800001</v>
       </c>
       <c r="Q78">
-        <v>62.62728153599997</v>
+        <v>60.86208787199999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.203916138563367</v>
+        <v>0.2107907532835133</v>
       </c>
       <c r="T78">
-        <v>2.666065249239741</v>
+        <v>2.781981129641469</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.159642241772861</v>
+        <v>0.1575689659056811</v>
       </c>
       <c r="W78">
-        <v>0.123364518907744</v>
+        <v>0.123668875805046</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8869013431825614</v>
+        <v>0.8753831439204505</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1437069076250935</v>
+        <v>0.1447169076250935</v>
       </c>
       <c r="C79">
-        <v>-388.6034247775508</v>
+        <v>-409.2980502317509</v>
       </c>
       <c r="D79">
-        <v>590.6245752224494</v>
+        <v>584.5939497682492</v>
       </c>
       <c r="E79">
-        <v>825.6280000000002</v>
+        <v>840.2920000000001</v>
       </c>
       <c r="F79">
-        <v>1129.128</v>
+        <v>1143.792</v>
       </c>
       <c r="G79">
         <v>149.9</v>
@@ -7765,37 +7765,37 @@
         <v>145.1</v>
       </c>
       <c r="M79">
-        <v>165.7559904</v>
+        <v>167.9086656</v>
       </c>
       <c r="N79">
-        <v>-20.65599040000001</v>
+        <v>-22.80866560000001</v>
       </c>
       <c r="O79">
-        <v>-3.718078272000001</v>
+        <v>-4.105559808000002</v>
       </c>
       <c r="P79">
-        <v>-16.93791212800001</v>
+        <v>-18.70310579200001</v>
       </c>
       <c r="Q79">
-        <v>60.86208787199999</v>
+        <v>59.09689420799999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2107907532835133</v>
+        <v>0.2182903329782185</v>
       </c>
       <c r="T79">
-        <v>2.781981129641469</v>
+        <v>2.908434817352445</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1575689659056811</v>
+        <v>0.1555488509581723</v>
       </c>
       <c r="W79">
-        <v>0.123668875805046</v>
+        <v>0.1239654286793403</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8753831439204505</v>
+        <v>0.8641602831009574</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1447169076250935</v>
+        <v>0.1457269076250935</v>
       </c>
       <c r="C80">
-        <v>-409.2980502317509</v>
+        <v>-429.8707679465147</v>
       </c>
       <c r="D80">
-        <v>584.5939497682492</v>
+        <v>578.6852320534855</v>
       </c>
       <c r="E80">
-        <v>840.2920000000001</v>
+        <v>854.9560000000001</v>
       </c>
       <c r="F80">
-        <v>1143.792</v>
+        <v>1158.456</v>
       </c>
       <c r="G80">
         <v>149.9</v>
@@ -7847,37 +7847,37 @@
         <v>145.1</v>
       </c>
       <c r="M80">
-        <v>167.9086656</v>
+        <v>170.0613408</v>
       </c>
       <c r="N80">
-        <v>-22.80866560000001</v>
+        <v>-24.96134080000002</v>
       </c>
       <c r="O80">
-        <v>-4.105559808000002</v>
+        <v>-4.493041344000003</v>
       </c>
       <c r="P80">
-        <v>-18.70310579200001</v>
+        <v>-20.46829945600001</v>
       </c>
       <c r="Q80">
-        <v>59.09689420799999</v>
+        <v>57.33170054399999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2182903329782185</v>
+        <v>0.2265041583581337</v>
       </c>
       <c r="T80">
-        <v>2.908434817352445</v>
+        <v>3.046931713416847</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1555488509581723</v>
+        <v>0.1535798781612334</v>
       </c>
       <c r="W80">
-        <v>0.1239654286793403</v>
+        <v>0.1242544738859309</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8641602831009574</v>
+        <v>0.8532215453401858</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1457269076250935</v>
+        <v>0.1467369076250935</v>
       </c>
       <c r="C81">
-        <v>-429.8707679465147</v>
+        <v>-450.3252374400411</v>
       </c>
       <c r="D81">
-        <v>578.6852320534855</v>
+        <v>572.8947625599591</v>
       </c>
       <c r="E81">
-        <v>854.9560000000001</v>
+        <v>869.6200000000001</v>
       </c>
       <c r="F81">
-        <v>1158.456</v>
+        <v>1173.12</v>
       </c>
       <c r="G81">
         <v>149.9</v>
@@ -7929,37 +7929,37 @@
         <v>145.1</v>
       </c>
       <c r="M81">
-        <v>170.0613408</v>
+        <v>172.214016</v>
       </c>
       <c r="N81">
-        <v>-24.96134080000002</v>
+        <v>-27.11401600000002</v>
       </c>
       <c r="O81">
-        <v>-4.493041344000003</v>
+        <v>-4.880522880000004</v>
       </c>
       <c r="P81">
-        <v>-20.46829945600001</v>
+        <v>-22.23349312000002</v>
       </c>
       <c r="Q81">
-        <v>57.33170054399999</v>
+        <v>55.56650687999998</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2265041583581337</v>
+        <v>0.2355393662760404</v>
       </c>
       <c r="T81">
-        <v>3.046931713416847</v>
+        <v>3.19927829908769</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1535798781612334</v>
+        <v>0.151660129684218</v>
       </c>
       <c r="W81">
-        <v>0.1242544738859309</v>
+        <v>0.1245362929623568</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8532215453401858</v>
+        <v>0.8425562760234335</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1467369076250935</v>
+        <v>0.1477469076250935</v>
       </c>
       <c r="C82">
-        <v>-450.3252374400411</v>
+        <v>-470.6649732094224</v>
       </c>
       <c r="D82">
-        <v>572.8947625599591</v>
+        <v>567.2190267905777</v>
       </c>
       <c r="E82">
-        <v>869.6200000000001</v>
+        <v>884.2840000000001</v>
       </c>
       <c r="F82">
-        <v>1173.12</v>
+        <v>1187.784</v>
       </c>
       <c r="G82">
         <v>149.9</v>
@@ -8011,37 +8011,37 @@
         <v>145.1</v>
       </c>
       <c r="M82">
-        <v>172.214016</v>
+        <v>174.3666912</v>
       </c>
       <c r="N82">
-        <v>-27.11401600000002</v>
+        <v>-29.2666912</v>
       </c>
       <c r="O82">
-        <v>-4.880522880000004</v>
+        <v>-5.268004415999999</v>
       </c>
       <c r="P82">
-        <v>-22.23349312000002</v>
+        <v>-23.998686784</v>
       </c>
       <c r="Q82">
-        <v>55.56650687999998</v>
+        <v>53.801313216</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2355393662760404</v>
+        <v>0.2455256487116214</v>
       </c>
       <c r="T82">
-        <v>3.19927829908769</v>
+        <v>3.367661367460725</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.151660129684218</v>
+        <v>0.149787782404166</v>
       </c>
       <c r="W82">
-        <v>0.1245362929623568</v>
+        <v>0.1248111535430684</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8425562760234335</v>
+        <v>0.8321543466898109</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1477469076250935</v>
+        <v>0.1487569076250935</v>
       </c>
       <c r="C83">
-        <v>-470.6649732094224</v>
+        <v>-490.8933518438761</v>
       </c>
       <c r="D83">
-        <v>567.2190267905777</v>
+        <v>561.654648156124</v>
       </c>
       <c r="E83">
-        <v>884.2840000000001</v>
+        <v>898.9480000000001</v>
       </c>
       <c r="F83">
-        <v>1187.784</v>
+        <v>1202.448</v>
       </c>
       <c r="G83">
         <v>149.9</v>
@@ -8093,37 +8093,37 @@
         <v>145.1</v>
       </c>
       <c r="M83">
-        <v>174.3666912</v>
+        <v>176.5193664</v>
       </c>
       <c r="N83">
-        <v>-29.2666912</v>
+        <v>-31.4193664</v>
       </c>
       <c r="O83">
-        <v>-5.268004415999999</v>
+        <v>-5.655485952</v>
       </c>
       <c r="P83">
-        <v>-23.998686784</v>
+        <v>-25.763880448</v>
       </c>
       <c r="Q83">
-        <v>53.801313216</v>
+        <v>52.036119552</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2455256487116214</v>
+        <v>0.2566215180844893</v>
       </c>
       <c r="T83">
-        <v>3.367661367460725</v>
+        <v>3.554753665652989</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.149787782404166</v>
+        <v>0.1479611021309444</v>
       </c>
       <c r="W83">
-        <v>0.1248111535430684</v>
+        <v>0.1250793102071774</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8321543466898109</v>
+        <v>0.8220061229496913</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1487569076250935</v>
+        <v>0.1497669076250935</v>
       </c>
       <c r="C84">
-        <v>-490.8933518438761</v>
+        <v>-511.0136187233649</v>
       </c>
       <c r="D84">
-        <v>561.654648156124</v>
+        <v>556.1983812766352</v>
       </c>
       <c r="E84">
-        <v>898.9480000000001</v>
+        <v>913.6120000000001</v>
       </c>
       <c r="F84">
-        <v>1202.448</v>
+        <v>1217.112</v>
       </c>
       <c r="G84">
         <v>149.9</v>
@@ -8175,37 +8175,37 @@
         <v>145.1</v>
       </c>
       <c r="M84">
-        <v>176.5193664</v>
+        <v>178.6720416</v>
       </c>
       <c r="N84">
-        <v>-31.4193664</v>
+        <v>-33.57204160000001</v>
       </c>
       <c r="O84">
-        <v>-5.655485952</v>
+        <v>-6.042967488</v>
       </c>
       <c r="P84">
-        <v>-25.763880448</v>
+        <v>-27.529074112</v>
       </c>
       <c r="Q84">
-        <v>52.036119552</v>
+        <v>50.27092588799999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2566215180844893</v>
+        <v>0.2690227838541652</v>
       </c>
       <c r="T84">
-        <v>3.554753665652989</v>
+        <v>3.763856822456106</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1479611021309444</v>
+        <v>0.1461784382498487</v>
       </c>
       <c r="W84">
-        <v>0.1250793102071774</v>
+        <v>0.1253410052649222</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8220061229496913</v>
+        <v>0.8121024347213817</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1497669076250935</v>
+        <v>0.1507769076250935</v>
       </c>
       <c r="C85">
-        <v>-511.0136187233649</v>
+        <v>-531.0288943305268</v>
       </c>
       <c r="D85">
-        <v>556.1983812766352</v>
+        <v>550.8471056694735</v>
       </c>
       <c r="E85">
-        <v>913.6120000000001</v>
+        <v>928.2760000000003</v>
       </c>
       <c r="F85">
-        <v>1217.112</v>
+        <v>1231.776</v>
       </c>
       <c r="G85">
         <v>149.9</v>
@@ -8257,37 +8257,37 @@
         <v>145.1</v>
       </c>
       <c r="M85">
-        <v>178.6720416</v>
+        <v>180.8247168000001</v>
       </c>
       <c r="N85">
-        <v>-33.57204160000001</v>
+        <v>-35.72471680000004</v>
       </c>
       <c r="O85">
-        <v>-6.042967488</v>
+        <v>-6.430449024000007</v>
       </c>
       <c r="P85">
-        <v>-27.529074112</v>
+        <v>-29.29426777600003</v>
       </c>
       <c r="Q85">
-        <v>50.27092588799999</v>
+        <v>48.50573222399996</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2690227838541652</v>
+        <v>0.2829742078450506</v>
       </c>
       <c r="T85">
-        <v>3.763856822456106</v>
+        <v>3.999097873859613</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1461784382498487</v>
+        <v>0.1444382187468743</v>
       </c>
       <c r="W85">
-        <v>0.1253410052649222</v>
+        <v>0.1255964694879589</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8121024347213817</v>
+        <v>0.8024345485937461</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1507769076250935</v>
+        <v>0.1990960412127789</v>
       </c>
       <c r="C86">
-        <v>-531.0288943305263</v>
+        <v>-719.3206975970753</v>
       </c>
       <c r="D86">
-        <v>550.8471056694738</v>
+        <v>377.2193024029248</v>
       </c>
       <c r="E86">
-        <v>928.2760000000001</v>
+        <v>942.9400000000001</v>
       </c>
       <c r="F86">
-        <v>1231.776</v>
+        <v>1246.44</v>
       </c>
       <c r="G86">
         <v>149.9</v>
@@ -8339,45 +8339,45 @@
         <v>145.1</v>
       </c>
       <c r="M86">
-        <v>180.8247168</v>
+        <v>250.285152</v>
       </c>
       <c r="N86">
-        <v>-35.72471680000001</v>
+        <v>-105.185152</v>
       </c>
       <c r="O86">
-        <v>-6.430449024000001</v>
+        <v>-18.93332736</v>
       </c>
       <c r="P86">
-        <v>-29.29426777600001</v>
+        <v>-86.25182464</v>
       </c>
       <c r="Q86">
-        <v>48.50573222399998</v>
+        <v>-8.451824639999998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2829742078450503</v>
+        <v>0.3081800456192896</v>
       </c>
       <c r="T86">
-        <v>3.99909787385961</v>
+        <v>4.4241045099845</v>
       </c>
       <c r="U86">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1444382187468743</v>
+        <v>0.1043529741628461</v>
       </c>
       <c r="W86">
-        <v>0.1255964694879589</v>
+        <v>0.1798459227881005</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.8024345485937462</v>
+        <v>0.5797387453491449</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1990960412127789</v>
+        <v>0.2006460412127789</v>
       </c>
       <c r="C87">
-        <v>-719.3206975970753</v>
+        <v>-737.7606411997991</v>
       </c>
       <c r="D87">
-        <v>377.2193024029248</v>
+        <v>373.4433588002009</v>
       </c>
       <c r="E87">
-        <v>942.9400000000001</v>
+        <v>957.604</v>
       </c>
       <c r="F87">
-        <v>1246.44</v>
+        <v>1261.104</v>
       </c>
       <c r="G87">
         <v>149.9</v>
@@ -8421,37 +8421,37 @@
         <v>145.1</v>
       </c>
       <c r="M87">
-        <v>250.285152</v>
+        <v>253.2296832</v>
       </c>
       <c r="N87">
-        <v>-105.185152</v>
+        <v>-108.1296832</v>
       </c>
       <c r="O87">
-        <v>-18.93332736</v>
+        <v>-19.463342976</v>
       </c>
       <c r="P87">
-        <v>-86.25182464</v>
+        <v>-88.666340224</v>
       </c>
       <c r="Q87">
-        <v>-8.451824639999998</v>
+        <v>-10.866340224</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3081800456192896</v>
+        <v>0.3269214774492388</v>
       </c>
       <c r="T87">
-        <v>4.4241045099845</v>
+        <v>4.740111974983392</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1043529741628461</v>
+        <v>0.1031395674865339</v>
       </c>
       <c r="W87">
-        <v>0.1798459227881005</v>
+        <v>0.180089574848704</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5797387453491449</v>
+        <v>0.5729975971474106</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2006460412127789</v>
+        <v>0.2021960412127789</v>
       </c>
       <c r="C88">
-        <v>-737.7606411997991</v>
+        <v>-756.1257400361361</v>
       </c>
       <c r="D88">
-        <v>373.4433588002009</v>
+        <v>369.7422599638639</v>
       </c>
       <c r="E88">
-        <v>957.604</v>
+        <v>972.268</v>
       </c>
       <c r="F88">
-        <v>1261.104</v>
+        <v>1275.768</v>
       </c>
       <c r="G88">
         <v>149.9</v>
@@ -8503,37 +8503,37 @@
         <v>145.1</v>
       </c>
       <c r="M88">
-        <v>253.2296832</v>
+        <v>256.1742144</v>
       </c>
       <c r="N88">
-        <v>-108.1296832</v>
+        <v>-111.0742144</v>
       </c>
       <c r="O88">
-        <v>-19.463342976</v>
+        <v>-19.993358592</v>
       </c>
       <c r="P88">
-        <v>-88.666340224</v>
+        <v>-91.08085580800001</v>
       </c>
       <c r="Q88">
-        <v>-10.866340224</v>
+        <v>-13.28085580800001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3269214774492388</v>
+        <v>0.3485462064837956</v>
       </c>
       <c r="T88">
-        <v>4.740111974983392</v>
+        <v>5.104735973059038</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1031395674865339</v>
+        <v>0.1019540552165737</v>
       </c>
       <c r="W88">
-        <v>0.180089574848704</v>
+        <v>0.180327625712512</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5729975971474106</v>
+        <v>0.5664114178698541</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2021960412127789</v>
+        <v>0.2037460412127789</v>
       </c>
       <c r="C89">
-        <v>-756.1257400361361</v>
+        <v>-774.4181975684901</v>
       </c>
       <c r="D89">
-        <v>369.7422599638639</v>
+        <v>366.11380243151</v>
       </c>
       <c r="E89">
-        <v>972.268</v>
+        <v>986.932</v>
       </c>
       <c r="F89">
-        <v>1275.768</v>
+        <v>1290.432</v>
       </c>
       <c r="G89">
         <v>149.9</v>
@@ -8585,37 +8585,37 @@
         <v>145.1</v>
       </c>
       <c r="M89">
-        <v>256.1742144</v>
+        <v>259.1187456</v>
       </c>
       <c r="N89">
-        <v>-111.0742144</v>
+        <v>-114.0187456</v>
       </c>
       <c r="O89">
-        <v>-19.993358592</v>
+        <v>-20.523374208</v>
       </c>
       <c r="P89">
-        <v>-91.08085580800001</v>
+        <v>-93.495371392</v>
       </c>
       <c r="Q89">
-        <v>-13.28085580800001</v>
+        <v>-15.695371392</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3485462064837956</v>
+        <v>0.373775057024112</v>
       </c>
       <c r="T89">
-        <v>5.104735973059038</v>
+        <v>5.530130637480625</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1019540552165737</v>
+        <v>0.1007954864072945</v>
       </c>
       <c r="W89">
-        <v>0.180327625712512</v>
+        <v>0.1805602663294153</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5664114178698541</v>
+        <v>0.5599749244849694</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2037460412127789</v>
+        <v>0.2052960412127789</v>
       </c>
       <c r="C90">
-        <v>-774.4181975684901</v>
+        <v>-792.6401316053091</v>
       </c>
       <c r="D90">
-        <v>366.11380243151</v>
+        <v>362.5558683946909</v>
       </c>
       <c r="E90">
-        <v>986.932</v>
+        <v>1001.596</v>
       </c>
       <c r="F90">
-        <v>1290.432</v>
+        <v>1305.096</v>
       </c>
       <c r="G90">
         <v>149.9</v>
@@ -8667,37 +8667,37 @@
         <v>145.1</v>
       </c>
       <c r="M90">
-        <v>259.1187456</v>
+        <v>262.0632768</v>
       </c>
       <c r="N90">
-        <v>-114.0187456</v>
+        <v>-116.9632768</v>
       </c>
       <c r="O90">
-        <v>-20.523374208</v>
+        <v>-21.05338982399999</v>
       </c>
       <c r="P90">
-        <v>-93.495371392</v>
+        <v>-95.90988697599997</v>
       </c>
       <c r="Q90">
-        <v>-15.695371392</v>
+        <v>-18.10988697599997</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.373775057024112</v>
+        <v>0.4035909712990312</v>
       </c>
       <c r="T90">
-        <v>5.530130637480625</v>
+        <v>6.032869786342499</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1007954864072945</v>
+        <v>0.09966295285215639</v>
       </c>
       <c r="W90">
-        <v>0.1805602663294153</v>
+        <v>0.180787679067287</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5599749244849694</v>
+        <v>0.5536830714008687</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2052960412127789</v>
+        <v>0.2068460412127789</v>
       </c>
       <c r="C91">
-        <v>-792.6401316053091</v>
+        <v>-810.793578423001</v>
       </c>
       <c r="D91">
-        <v>362.5558683946909</v>
+        <v>359.0664215769992</v>
       </c>
       <c r="E91">
-        <v>1001.596</v>
+        <v>1016.26</v>
       </c>
       <c r="F91">
-        <v>1305.096</v>
+        <v>1319.76</v>
       </c>
       <c r="G91">
         <v>149.9</v>
@@ -8749,37 +8749,37 @@
         <v>145.1</v>
       </c>
       <c r="M91">
-        <v>262.0632768</v>
+        <v>265.0078080000001</v>
       </c>
       <c r="N91">
-        <v>-116.9632768</v>
+        <v>-119.907808</v>
       </c>
       <c r="O91">
-        <v>-21.05338982399999</v>
+        <v>-21.58340544000001</v>
       </c>
       <c r="P91">
-        <v>-95.90988697599997</v>
+        <v>-98.32440256000004</v>
       </c>
       <c r="Q91">
-        <v>-18.10988697599997</v>
+        <v>-20.52440256000004</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4035909712990312</v>
+        <v>0.4393700684289345</v>
       </c>
       <c r="T91">
-        <v>6.032869786342499</v>
+        <v>6.636156764976752</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.09966295285215639</v>
+        <v>0.0985555867093546</v>
       </c>
       <c r="W91">
-        <v>0.180787679067287</v>
+        <v>0.1810100381887616</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5536830714008687</v>
+        <v>0.5475310372741923</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2068460412127789</v>
+        <v>0.2083960412127789</v>
       </c>
       <c r="C92">
-        <v>-810.793578423001</v>
+        <v>-828.8804966520864</v>
       </c>
       <c r="D92">
-        <v>359.0664215769992</v>
+        <v>355.6435033479138</v>
       </c>
       <c r="E92">
-        <v>1016.26</v>
+        <v>1030.924</v>
       </c>
       <c r="F92">
-        <v>1319.76</v>
+        <v>1334.424</v>
       </c>
       <c r="G92">
         <v>149.9</v>
@@ -8831,37 +8831,37 @@
         <v>145.1</v>
       </c>
       <c r="M92">
-        <v>265.0078080000001</v>
+        <v>267.9523392</v>
       </c>
       <c r="N92">
-        <v>-119.907808</v>
+        <v>-122.8523392</v>
       </c>
       <c r="O92">
-        <v>-21.58340544000001</v>
+        <v>-22.113421056</v>
       </c>
       <c r="P92">
-        <v>-98.32440256000004</v>
+        <v>-100.738918144</v>
       </c>
       <c r="Q92">
-        <v>-20.52440256000004</v>
+        <v>-22.93891814400001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4393700684289345</v>
+        <v>0.4831000760321494</v>
       </c>
       <c r="T92">
-        <v>6.636156764976752</v>
+        <v>7.373507516640835</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.0985555867093546</v>
+        <v>0.09747255828397709</v>
       </c>
       <c r="W92">
-        <v>0.1810100381887616</v>
+        <v>0.1812275102965774</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5475310372741923</v>
+        <v>0.5415142126887617</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2083960412127789</v>
+        <v>0.2099460412127789</v>
       </c>
       <c r="C93">
-        <v>-828.8804966520864</v>
+        <v>-846.9027709431775</v>
       </c>
       <c r="D93">
-        <v>355.6435033479138</v>
+        <v>352.2852290568226</v>
       </c>
       <c r="E93">
-        <v>1030.924</v>
+        <v>1045.588</v>
       </c>
       <c r="F93">
-        <v>1334.424</v>
+        <v>1349.088</v>
       </c>
       <c r="G93">
         <v>149.9</v>
@@ -8913,37 +8913,37 @@
         <v>145.1</v>
       </c>
       <c r="M93">
-        <v>267.9523392</v>
+        <v>270.8968704000001</v>
       </c>
       <c r="N93">
-        <v>-122.8523392</v>
+        <v>-125.7968704</v>
       </c>
       <c r="O93">
-        <v>-22.113421056</v>
+        <v>-22.64343667200001</v>
       </c>
       <c r="P93">
-        <v>-100.738918144</v>
+        <v>-103.153433728</v>
       </c>
       <c r="Q93">
-        <v>-22.93891814400001</v>
+        <v>-25.35343372800004</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4831000760321494</v>
+        <v>0.5377625855361682</v>
       </c>
       <c r="T93">
-        <v>7.373507516640835</v>
+        <v>8.295195956220942</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.09747255828397709</v>
+        <v>0.09641307395480342</v>
       </c>
       <c r="W93">
-        <v>0.1812275102965774</v>
+        <v>0.1814402547498755</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5415142126887617</v>
+        <v>0.5356281886377967</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2099460412127789</v>
+        <v>0.2114960412127789</v>
       </c>
       <c r="C94">
-        <v>-846.9027709431775</v>
+        <v>-864.8622154271944</v>
       </c>
       <c r="D94">
-        <v>352.2852290568226</v>
+        <v>348.9897845728058</v>
       </c>
       <c r="E94">
-        <v>1045.588</v>
+        <v>1060.252</v>
       </c>
       <c r="F94">
-        <v>1349.088</v>
+        <v>1363.752</v>
       </c>
       <c r="G94">
         <v>149.9</v>
@@ -8995,37 +8995,37 @@
         <v>145.1</v>
       </c>
       <c r="M94">
-        <v>270.8968704000001</v>
+        <v>273.8414016</v>
       </c>
       <c r="N94">
-        <v>-125.7968704</v>
+        <v>-128.7414016</v>
       </c>
       <c r="O94">
-        <v>-22.64343667200001</v>
+        <v>-23.173452288</v>
       </c>
       <c r="P94">
-        <v>-103.153433728</v>
+        <v>-105.567949312</v>
       </c>
       <c r="Q94">
-        <v>-25.35343372800004</v>
+        <v>-27.76794931200001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5377625855361682</v>
+        <v>0.608042954898478</v>
       </c>
       <c r="T94">
-        <v>8.295195956220942</v>
+        <v>9.480223949966792</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.09641307395480342</v>
+        <v>0.09537637423485931</v>
       </c>
       <c r="W94">
-        <v>0.1814402547498755</v>
+        <v>0.1816484240536403</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5356281886377967</v>
+        <v>0.5298687457492184</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2114960412127789</v>
+        <v>0.2130460412127789</v>
       </c>
       <c r="C95">
-        <v>-864.8622154271944</v>
+        <v>-882.7605769831707</v>
       </c>
       <c r="D95">
-        <v>348.9897845728058</v>
+        <v>345.7554230168295</v>
       </c>
       <c r="E95">
-        <v>1060.252</v>
+        <v>1074.916</v>
       </c>
       <c r="F95">
-        <v>1363.752</v>
+        <v>1378.416</v>
       </c>
       <c r="G95">
         <v>149.9</v>
@@ -9077,37 +9077,37 @@
         <v>145.1</v>
       </c>
       <c r="M95">
-        <v>273.8414016</v>
+        <v>276.7859328000001</v>
       </c>
       <c r="N95">
-        <v>-128.7414016</v>
+        <v>-131.6859328</v>
       </c>
       <c r="O95">
-        <v>-23.173452288</v>
+        <v>-23.70346790400001</v>
       </c>
       <c r="P95">
-        <v>-105.567949312</v>
+        <v>-107.982464896</v>
       </c>
       <c r="Q95">
-        <v>-27.76794931200001</v>
+        <v>-30.18246489600004</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.608042954898478</v>
+        <v>0.7017501140482246</v>
       </c>
       <c r="T95">
-        <v>9.480223949966792</v>
+        <v>11.06026127496126</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.09537637423485931</v>
+        <v>0.09436173195576505</v>
       </c>
       <c r="W95">
-        <v>0.1816484240536403</v>
+        <v>0.1818521642232824</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5298687457492184</v>
+        <v>0.5242318441986947</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2130460412127789</v>
+        <v>0.2145960412127789</v>
       </c>
       <c r="C96">
-        <v>-882.7605769831707</v>
+        <v>-900.5995383260171</v>
       </c>
       <c r="D96">
-        <v>345.7554230168295</v>
+        <v>342.5804616739831</v>
       </c>
       <c r="E96">
-        <v>1074.916</v>
+        <v>1089.58</v>
       </c>
       <c r="F96">
-        <v>1378.416</v>
+        <v>1393.08</v>
       </c>
       <c r="G96">
         <v>149.9</v>
@@ -9159,37 +9159,37 @@
         <v>145.1</v>
       </c>
       <c r="M96">
-        <v>276.7859328000001</v>
+        <v>279.730464</v>
       </c>
       <c r="N96">
-        <v>-131.6859328</v>
+        <v>-134.630464</v>
       </c>
       <c r="O96">
-        <v>-23.70346790400001</v>
+        <v>-24.23348352</v>
       </c>
       <c r="P96">
-        <v>-107.982464896</v>
+        <v>-110.39698048</v>
       </c>
       <c r="Q96">
-        <v>-30.18246489600004</v>
+        <v>-32.59698048000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7017501140482246</v>
+        <v>0.8329401368578697</v>
       </c>
       <c r="T96">
-        <v>11.06026127496126</v>
+        <v>13.27231352995352</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.09436173195576505</v>
+        <v>0.09336845056675701</v>
       </c>
       <c r="W96">
-        <v>0.1818521642232824</v>
+        <v>0.1820516151261952</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5242318441986947</v>
+        <v>0.5187136142597611</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2145960412127789</v>
+        <v>0.2161460412127789</v>
       </c>
       <c r="C97">
-        <v>-900.5995383260171</v>
+        <v>-918.3807209257078</v>
       </c>
       <c r="D97">
-        <v>342.5804616739831</v>
+        <v>339.4632790742924</v>
       </c>
       <c r="E97">
-        <v>1089.58</v>
+        <v>1104.244</v>
       </c>
       <c r="F97">
-        <v>1393.08</v>
+        <v>1407.744</v>
       </c>
       <c r="G97">
         <v>149.9</v>
@@ -9241,37 +9241,37 @@
         <v>145.1</v>
       </c>
       <c r="M97">
-        <v>279.730464</v>
+        <v>282.6749952</v>
       </c>
       <c r="N97">
-        <v>-134.630464</v>
+        <v>-137.5749952</v>
       </c>
       <c r="O97">
-        <v>-24.23348352</v>
+        <v>-24.763499136</v>
       </c>
       <c r="P97">
-        <v>-110.39698048</v>
+        <v>-112.811496064</v>
       </c>
       <c r="Q97">
-        <v>-32.59698048000001</v>
+        <v>-35.011496064</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8329401368578697</v>
+        <v>1.029725171072338</v>
       </c>
       <c r="T97">
-        <v>13.27231352995352</v>
+        <v>16.59039191244191</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.09336845056675701</v>
+        <v>0.09239586254001997</v>
       </c>
       <c r="W97">
-        <v>0.1820516151261952</v>
+        <v>0.182246910801964</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5187136142597611</v>
+        <v>0.5133103474445553</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2161460412127789</v>
+        <v>0.2176960412127789</v>
       </c>
       <c r="C98">
-        <v>-918.3807209257079</v>
+        <v>-936.1056877685326</v>
       </c>
       <c r="D98">
-        <v>339.4632790742922</v>
+        <v>336.4023122314675</v>
       </c>
       <c r="E98">
-        <v>1104.244</v>
+        <v>1118.908</v>
       </c>
       <c r="F98">
-        <v>1407.744</v>
+        <v>1422.408</v>
       </c>
       <c r="G98">
         <v>149.9</v>
@@ -9323,37 +9323,37 @@
         <v>145.1</v>
       </c>
       <c r="M98">
-        <v>282.6749952</v>
+        <v>285.6195264</v>
       </c>
       <c r="N98">
-        <v>-137.5749952</v>
+        <v>-140.5195264</v>
       </c>
       <c r="O98">
-        <v>-24.763499136</v>
+        <v>-25.293514752</v>
       </c>
       <c r="P98">
-        <v>-112.811496064</v>
+        <v>-115.226011648</v>
       </c>
       <c r="Q98">
-        <v>-35.011496064</v>
+        <v>-37.42601164800001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.029725171072335</v>
+        <v>1.357700228096447</v>
       </c>
       <c r="T98">
-        <v>16.59039191244186</v>
+        <v>22.12052254992248</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.09239586254001997</v>
+        <v>0.09144332787465892</v>
       </c>
       <c r="W98">
-        <v>0.182246910801964</v>
+        <v>0.1824381797627685</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5133103474445553</v>
+        <v>0.5080184881925496</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2176960412127789</v>
+        <v>0.2192460412127789</v>
       </c>
       <c r="C99">
-        <v>-936.1056877685326</v>
+        <v>-953.775945970293</v>
       </c>
       <c r="D99">
-        <v>336.4023122314675</v>
+        <v>333.3960540297071</v>
       </c>
       <c r="E99">
-        <v>1118.908</v>
+        <v>1133.572</v>
       </c>
       <c r="F99">
-        <v>1422.408</v>
+        <v>1437.072</v>
       </c>
       <c r="G99">
         <v>149.9</v>
@@ -9405,37 +9405,37 @@
         <v>145.1</v>
       </c>
       <c r="M99">
-        <v>285.6195264</v>
+        <v>288.5640576</v>
       </c>
       <c r="N99">
-        <v>-140.5195264</v>
+        <v>-143.4640576</v>
       </c>
       <c r="O99">
-        <v>-25.293514752</v>
+        <v>-25.823530368</v>
       </c>
       <c r="P99">
-        <v>-115.226011648</v>
+        <v>-117.640527232</v>
       </c>
       <c r="Q99">
-        <v>-37.42601164800001</v>
+        <v>-39.840527232</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.357700228096447</v>
+        <v>2.01365034214467</v>
       </c>
       <c r="T99">
-        <v>22.12052254992248</v>
+        <v>33.18078382488372</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.09144332787465892</v>
+        <v>0.09051023269226446</v>
       </c>
       <c r="W99">
-        <v>0.1824381797627685</v>
+        <v>0.1826255452753933</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5080184881925496</v>
+        <v>0.5028346260681358</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2192460412127789</v>
+        <v>0.2560146436358561</v>
       </c>
       <c r="C100">
-        <v>-953.775945970293</v>
+        <v>-1026.75418492158</v>
       </c>
       <c r="D100">
-        <v>333.3960540297071</v>
+        <v>275.0818150784196</v>
       </c>
       <c r="E100">
-        <v>1133.572</v>
+        <v>1148.236</v>
       </c>
       <c r="F100">
-        <v>1437.072</v>
+        <v>1451.736</v>
       </c>
       <c r="G100">
         <v>149.9</v>
@@ -9487,129 +9487,47 @@
         <v>145.1</v>
       </c>
       <c r="M100">
-        <v>288.5640576</v>
+        <v>342.3193488000001</v>
       </c>
       <c r="N100">
-        <v>-143.4640576</v>
+        <v>-197.2193488</v>
       </c>
       <c r="O100">
-        <v>-25.823530368</v>
+        <v>-35.499482784</v>
       </c>
       <c r="P100">
-        <v>-117.640527232</v>
+        <v>-161.719866016</v>
       </c>
       <c r="Q100">
-        <v>-39.840527232</v>
+        <v>-83.91986601600003</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.01365034214467</v>
+        <v>4.038360926597067</v>
       </c>
       <c r="T100">
-        <v>33.18078382488372</v>
+        <v>67.3203130217285</v>
       </c>
       <c r="U100">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09051023269226446</v>
+        <v>0.07629717715798598</v>
       </c>
       <c r="W100">
-        <v>0.1826255452753933</v>
+        <v>0.2178091256261469</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.5028346260681358</v>
+        <v>0.4238732064332555</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2560146436358561</v>
-      </c>
-      <c r="C101">
-        <v>-1026.75418492158</v>
-      </c>
-      <c r="D101">
-        <v>275.0818150784196</v>
-      </c>
-      <c r="E101">
-        <v>1148.236</v>
-      </c>
-      <c r="F101">
-        <v>1451.736</v>
-      </c>
-      <c r="G101">
-        <v>149.9</v>
-      </c>
-      <c r="H101">
-        <v>1162.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>222.9</v>
-      </c>
-      <c r="K101">
-        <v>77.8</v>
-      </c>
-      <c r="L101">
-        <v>145.1</v>
-      </c>
-      <c r="M101">
-        <v>342.3193488000001</v>
-      </c>
-      <c r="N101">
-        <v>-197.2193488</v>
-      </c>
-      <c r="O101">
-        <v>-35.499482784</v>
-      </c>
-      <c r="P101">
-        <v>-161.719866016</v>
-      </c>
-      <c r="Q101">
-        <v>-83.91986601600003</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.038360926597067</v>
-      </c>
-      <c r="T101">
-        <v>67.3203130217285</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07629717715798598</v>
-      </c>
-      <c r="W101">
-        <v>0.2178091256261469</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4238732064332555</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
